--- a/AMZN.xlsx
+++ b/AMZN.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26350EDB-9A9B-4946-A13F-7D2C495A165F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{489435C2-0125-4C49-9097-4B2D1F6259DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="50490" yWindow="680" windowWidth="24340" windowHeight="15680" xr2:uid="{319C79D3-530A-422D-B7D4-1569BBD88715}"/>
+    <workbookView xWindow="500" yWindow="1650" windowWidth="20990" windowHeight="18600" activeTab="1" xr2:uid="{319C79D3-530A-422D-B7D4-1569BBD88715}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -49,6 +49,9 @@
     <author>tc={A64624BB-B1AF-4371-B81E-B4367444230E}</author>
     <author>tc={C3C93262-255F-49A7-9F98-C9410B7BFA17}</author>
     <author>tc={C73FBD69-CAB6-4173-B10B-D5EF91565E7C}</author>
+    <author>tc={DC94B1A5-047E-4549-85B0-C148999B91DA}</author>
+    <author>tc={EB7BE6C5-F5DE-4A1D-8080-A5192FAB888F}</author>
+    <author>tc={4315BC09-5142-4247-8B90-11C426488D07}</author>
     <author>tc={BC0611F9-311A-4928-9AD6-94F49AE6B822}</author>
     <author>tc={1123E429-DC3C-402F-A940-60A8A504E208}</author>
     <author>tc={F0CECC32-58CA-41B9-9B42-426709AD1A9F}</author>
@@ -56,6 +59,7 @@
     <author>tc={4DD78E31-7CCE-477B-B706-40FDCE9AC3DE}</author>
     <author>tc={D6FB59F6-3F25-4686-97A0-9B49BDAE85AA}</author>
     <author>tc={93C7E41E-ABCA-41C7-84BA-68723DC06A79}</author>
+    <author>tc={4E2C1DBA-1CFC-4CE9-926C-4DA526205B50}</author>
     <author>tc={7DD33F83-8D06-4AB5-AE42-CC8AE1143AEE}</author>
     <author>tc={9ABE8371-ABDF-42F1-936F-09DADC3E4649}</author>
   </authors>
@@ -149,7 +153,32 @@
     Q125 guidance: 159-164B</t>
       </text>
     </comment>
-    <comment ref="Y28" authorId="11" shapeId="0" xr:uid="{BC0611F9-311A-4928-9AD6-94F49AE6B822}">
+    <comment ref="AN20" authorId="11" shapeId="0" xr:uid="{DC94B1A5-047E-4549-85B0-C148999B91DA}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    7/30/26 consensus: 197030
+Q1 guide: 194-199</t>
+      </text>
+    </comment>
+    <comment ref="AO20" authorId="12" shapeId="0" xr:uid="{EB7BE6C5-F5DE-4A1D-8080-A5192FAB888F}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    7/30/26 consensus: 203910</t>
+      </text>
+    </comment>
+    <comment ref="AP20" authorId="13" shapeId="0" xr:uid="{4315BC09-5142-4247-8B90-11C426488D07}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    7/30/26 consensus: 242760</t>
+      </text>
+    </comment>
+    <comment ref="Y28" authorId="14" shapeId="0" xr:uid="{BC0611F9-311A-4928-9AD6-94F49AE6B822}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -157,7 +186,7 @@
     Q222 guidance: 0.0-3.5B</t>
       </text>
     </comment>
-    <comment ref="Z28" authorId="12" shapeId="0" xr:uid="{1123E429-DC3C-402F-A940-60A8A504E208}">
+    <comment ref="Z28" authorId="15" shapeId="0" xr:uid="{1123E429-DC3C-402F-A940-60A8A504E208}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -165,7 +194,7 @@
     Q3 guidance: 0-4B</t>
       </text>
     </comment>
-    <comment ref="AA28" authorId="13" shapeId="0" xr:uid="{F0CECC32-58CA-41B9-9B42-426709AD1A9F}">
+    <comment ref="AA28" authorId="16" shapeId="0" xr:uid="{F0CECC32-58CA-41B9-9B42-426709AD1A9F}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -173,7 +202,7 @@
     Q4 guidance 0-4B</t>
       </text>
     </comment>
-    <comment ref="AB28" authorId="14" shapeId="0" xr:uid="{EEC432E6-C1EF-4C03-8D2E-1AD7704A7DFC}">
+    <comment ref="AB28" authorId="17" shapeId="0" xr:uid="{EEC432E6-C1EF-4C03-8D2E-1AD7704A7DFC}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -182,7 +211,7 @@
 I estimated 5.6B prior to guidance</t>
       </text>
     </comment>
-    <comment ref="AF28" authorId="15" shapeId="0" xr:uid="{4DD78E31-7CCE-477B-B706-40FDCE9AC3DE}">
+    <comment ref="AF28" authorId="18" shapeId="0" xr:uid="{4DD78E31-7CCE-477B-B706-40FDCE9AC3DE}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -190,7 +219,7 @@
     10-14B</t>
       </text>
     </comment>
-    <comment ref="AI28" authorId="16" shapeId="0" xr:uid="{D6FB59F6-3F25-4686-97A0-9B49BDAE85AA}">
+    <comment ref="AI28" authorId="19" shapeId="0" xr:uid="{D6FB59F6-3F25-4686-97A0-9B49BDAE85AA}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -198,7 +227,7 @@
     Q424: 14-18B</t>
       </text>
     </comment>
-    <comment ref="AJ28" authorId="17" shapeId="0" xr:uid="{93C7E41E-ABCA-41C7-84BA-68723DC06A79}">
+    <comment ref="AJ28" authorId="20" shapeId="0" xr:uid="{93C7E41E-ABCA-41C7-84BA-68723DC06A79}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -206,7 +235,15 @@
     Q125 guidance: 13.0-17.5B</t>
       </text>
     </comment>
-    <comment ref="Y36" authorId="18" shapeId="0" xr:uid="{7DD33F83-8D06-4AB5-AE42-CC8AE1143AEE}">
+    <comment ref="AN28" authorId="21" shapeId="0" xr:uid="{4E2C1DBA-1CFC-4CE9-926C-4DA526205B50}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Q1 guide: 20-24B</t>
+      </text>
+    </comment>
+    <comment ref="Y36" authorId="22" shapeId="0" xr:uid="{7DD33F83-8D06-4AB5-AE42-CC8AE1143AEE}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -214,7 +251,7 @@
     +19% net of FX</t>
       </text>
     </comment>
-    <comment ref="AE45" authorId="19" shapeId="0" xr:uid="{9ABE8371-ABDF-42F1-936F-09DADC3E4649}">
+    <comment ref="AE45" authorId="23" shapeId="0" xr:uid="{9ABE8371-ABDF-42F1-936F-09DADC3E4649}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -834,16 +871,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>36</xdr:col>
-      <xdr:colOff>33839</xdr:colOff>
+      <xdr:col>40</xdr:col>
+      <xdr:colOff>43609</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>29308</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>36</xdr:col>
-      <xdr:colOff>33839</xdr:colOff>
+      <xdr:col>40</xdr:col>
+      <xdr:colOff>43609</xdr:colOff>
       <xdr:row>114</xdr:row>
-      <xdr:rowOff>107462</xdr:rowOff>
+      <xdr:rowOff>136770</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -858,8 +895,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="23138070" y="0"/>
-          <a:ext cx="0" cy="18351500"/>
+          <a:off x="25590147" y="29308"/>
+          <a:ext cx="0" cy="18512693"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -1272,6 +1309,16 @@
   <threadedComment ref="AJ20" dT="2025-05-23T17:58:48.43" personId="{9B8D1A3E-D1D5-4929-A5A0-67791399E886}" id="{C73FBD69-CAB6-4173-B10B-D5EF91565E7C}">
     <text>Q125 guidance: 159-164B</text>
   </threadedComment>
+  <threadedComment ref="AN20" dT="2026-07-30T19:55:02.87" personId="{9B8D1A3E-D1D5-4929-A5A0-67791399E886}" id="{DC94B1A5-047E-4549-85B0-C148999B91DA}">
+    <text>7/30/26 consensus: 197030
+Q1 guide: 194-199</text>
+  </threadedComment>
+  <threadedComment ref="AO20" dT="2026-07-30T19:55:11.60" personId="{9B8D1A3E-D1D5-4929-A5A0-67791399E886}" id="{EB7BE6C5-F5DE-4A1D-8080-A5192FAB888F}">
+    <text>7/30/26 consensus: 203910</text>
+  </threadedComment>
+  <threadedComment ref="AP20" dT="2026-07-30T19:55:24.33" personId="{9B8D1A3E-D1D5-4929-A5A0-67791399E886}" id="{4315BC09-5142-4247-8B90-11C426488D07}">
+    <text>7/30/26 consensus: 242760</text>
+  </threadedComment>
   <threadedComment ref="Y28" dT="2022-07-29T15:10:25.65" personId="{9B8D1A3E-D1D5-4929-A5A0-67791399E886}" id="{BC0611F9-311A-4928-9AD6-94F49AE6B822}">
     <text>Q222 guidance: 0.0-3.5B</text>
   </threadedComment>
@@ -1294,6 +1341,9 @@
   <threadedComment ref="AJ28" dT="2025-05-23T17:59:02.76" personId="{9B8D1A3E-D1D5-4929-A5A0-67791399E886}" id="{93C7E41E-ABCA-41C7-84BA-68723DC06A79}">
     <text>Q125 guidance: 13.0-17.5B</text>
   </threadedComment>
+  <threadedComment ref="AN28" dT="2026-07-30T19:57:40.52" personId="{9B8D1A3E-D1D5-4929-A5A0-67791399E886}" id="{4E2C1DBA-1CFC-4CE9-926C-4DA526205B50}">
+    <text>Q1 guide: 20-24B</text>
+  </threadedComment>
   <threadedComment ref="Y36" dT="2022-12-19T01:32:23.85" personId="{9B8D1A3E-D1D5-4929-A5A0-67791399E886}" id="{7DD33F83-8D06-4AB5-AE42-CC8AE1143AEE}">
     <text>+19% net of FX</text>
   </threadedComment>
@@ -1316,7 +1366,7 @@
         <v>1</v>
       </c>
       <c r="K2" s="1">
-        <v>226</v>
+        <v>237.14</v>
       </c>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.25">
@@ -1324,10 +1374,10 @@
         <v>2</v>
       </c>
       <c r="K3" s="2">
-        <v>10806</v>
+        <v>10874</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>120</v>
+        <v>155</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.25">
@@ -1339,7 +1389,7 @@
       </c>
       <c r="K4" s="2">
         <f>K3*K2</f>
-        <v>2442156</v>
+        <v>2578660.36</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.25">
@@ -1376,7 +1426,7 @@
       </c>
       <c r="K7" s="2">
         <f>K4-K5+K6</f>
-        <v>2399694</v>
+        <v>2536198.36</v>
       </c>
       <c r="L7" s="3"/>
     </row>
@@ -1943,12 +1993,17 @@
         <v>100068</v>
       </c>
       <c r="AK3" s="2">
-        <f>+AG3*1.07</f>
-        <v>102224.59000000001</v>
+        <v>106267</v>
       </c>
       <c r="AL3" s="2">
         <f>+AH3*1.07</f>
         <v>123677.02</v>
+      </c>
+      <c r="AM3" s="2">
+        <v>104143</v>
+      </c>
+      <c r="AN3" s="2">
+        <v>116177</v>
       </c>
       <c r="BK3" s="2">
         <v>50834</v>
@@ -2159,12 +2214,17 @@
         <v>36761</v>
       </c>
       <c r="AK6" s="2">
-        <f>+AG6*1.07</f>
-        <v>38400.160000000003</v>
+        <v>40896</v>
       </c>
       <c r="AL6" s="2">
         <f>+AH6*1.07</f>
         <v>46459.4</v>
+      </c>
+      <c r="AM6" s="2">
+        <v>39789</v>
+      </c>
+      <c r="AN6" s="2">
+        <v>42197</v>
       </c>
       <c r="BK6" s="2">
         <v>33510</v>
@@ -2375,15 +2435,17 @@
         <v>30873</v>
       </c>
       <c r="AK9" s="4">
-        <f>+AG9*1.1</f>
-        <v>30197.200000000001</v>
+        <v>33006</v>
       </c>
       <c r="AL9" s="4">
-        <f>+AH9*1.1</f>
-        <v>31664.600000000002</v>
-      </c>
-      <c r="AM9" s="4"/>
-      <c r="AN9" s="4"/>
+        <v>35579</v>
+      </c>
+      <c r="AM9" s="4">
+        <v>37587</v>
+      </c>
+      <c r="AN9" s="4">
+        <v>42232</v>
+      </c>
       <c r="AO9" s="4"/>
       <c r="AP9" s="4"/>
       <c r="BK9" s="2">
@@ -2427,27 +2489,27 @@
       </c>
       <c r="BV9" s="2">
         <f>SUM(AI9:AL9)</f>
-        <v>122001.8</v>
+        <v>128725</v>
       </c>
       <c r="BW9" s="2">
         <f>+BV9*1.2</f>
-        <v>146402.16</v>
+        <v>154470</v>
       </c>
       <c r="BX9" s="2">
         <f>+BW9*1.2</f>
-        <v>175682.592</v>
+        <v>185364</v>
       </c>
       <c r="BY9" s="2">
         <f>+BX9*1.15</f>
-        <v>202034.98079999999</v>
+        <v>213168.59999999998</v>
       </c>
       <c r="BZ9" s="2">
         <f>+BY9*1.1</f>
-        <v>222238.47888000001</v>
+        <v>234485.46</v>
       </c>
       <c r="CA9" s="2">
         <f>+BZ9*1.1</f>
-        <v>244462.32676800003</v>
+        <v>257934.00600000002</v>
       </c>
     </row>
     <row r="11" spans="1:89" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2542,6 +2604,18 @@
       <c r="AJ11" s="2">
         <v>61485</v>
       </c>
+      <c r="AK11" s="2">
+        <v>67407</v>
+      </c>
+      <c r="AL11" s="2">
+        <v>82988</v>
+      </c>
+      <c r="AM11" s="2">
+        <v>64254</v>
+      </c>
+      <c r="AN11" s="2">
+        <v>70432</v>
+      </c>
       <c r="BO11" s="2">
         <f>26939+27165+29061+39822</f>
         <v>122987</v>
@@ -2687,6 +2761,18 @@
       <c r="AJ12" s="2">
         <v>5595</v>
       </c>
+      <c r="AK12" s="2">
+        <v>5578</v>
+      </c>
+      <c r="AL12" s="2">
+        <v>5855</v>
+      </c>
+      <c r="AM12" s="2">
+        <v>5785</v>
+      </c>
+      <c r="AN12" s="2">
+        <v>5794</v>
+      </c>
       <c r="BO12" s="2">
         <f>4263+4312+4248+4401</f>
         <v>17224</v>
@@ -2832,6 +2918,18 @@
       <c r="AJ13" s="2">
         <v>40348</v>
       </c>
+      <c r="AK13" s="2">
+        <v>42486</v>
+      </c>
+      <c r="AL13" s="2">
+        <v>52816</v>
+      </c>
+      <c r="AM13" s="2">
+        <v>41578</v>
+      </c>
+      <c r="AN13" s="2">
+        <v>46780</v>
+      </c>
       <c r="BO13" s="2">
         <f>9265+9702+10395+13383</f>
         <v>42745</v>
@@ -2960,22 +3058,34 @@
         <v>10488</v>
       </c>
       <c r="AE14" s="4">
-        <v>11824</v>
+        <v>10722</v>
       </c>
       <c r="AF14" s="4">
-        <v>12771</v>
+        <v>10866</v>
       </c>
       <c r="AG14" s="4">
-        <v>14331</v>
+        <v>11278</v>
       </c>
       <c r="AH14" s="2">
-        <v>17288</v>
+        <v>11508</v>
       </c>
       <c r="AI14" s="2">
-        <v>13921</v>
+        <v>11715</v>
       </c>
       <c r="AJ14" s="2">
-        <v>15694</v>
+        <v>12208</v>
+      </c>
+      <c r="AK14" s="2">
+        <v>12574</v>
+      </c>
+      <c r="AL14" s="2">
+        <v>13122</v>
+      </c>
+      <c r="AM14" s="2">
+        <v>13427</v>
+      </c>
+      <c r="AN14" s="2">
+        <v>13730</v>
       </c>
       <c r="BO14" s="2">
         <f>3102+3408+3698+3959</f>
@@ -3003,31 +3113,31 @@
       </c>
       <c r="BU14" s="2">
         <f t="shared" si="6"/>
-        <v>56214</v>
+        <v>44374</v>
       </c>
       <c r="BV14" s="2">
         <f t="shared" ref="BV14:BX14" si="10">+BU14*1.1</f>
-        <v>61835.4</v>
+        <v>48811.4</v>
       </c>
       <c r="BW14" s="2">
         <f t="shared" si="10"/>
-        <v>68018.94</v>
+        <v>53692.540000000008</v>
       </c>
       <c r="BX14" s="2">
         <f t="shared" si="10"/>
-        <v>74820.834000000003</v>
+        <v>59061.794000000016</v>
       </c>
       <c r="BY14" s="2">
         <f t="shared" ref="BY14:CA14" si="11">+BX14*1.05</f>
-        <v>78561.875700000004</v>
+        <v>62014.88370000002</v>
       </c>
       <c r="BZ14" s="2">
         <f t="shared" si="11"/>
-        <v>82489.969485000009</v>
+        <v>65115.627885000024</v>
       </c>
       <c r="CA14" s="2">
         <f t="shared" si="11"/>
-        <v>86614.467959250018</v>
+        <v>68371.409279250031</v>
       </c>
     </row>
     <row r="15" spans="1:89" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3105,22 +3215,34 @@
         <v>14654</v>
       </c>
       <c r="AE15" s="4">
-        <v>10722</v>
+        <v>11824</v>
       </c>
       <c r="AF15" s="4">
-        <v>10866</v>
+        <v>12771</v>
       </c>
       <c r="AG15" s="4">
-        <v>11278</v>
+        <v>14331</v>
       </c>
       <c r="AH15" s="2">
-        <v>11508</v>
+        <v>17288</v>
       </c>
       <c r="AI15" s="2">
-        <v>11715</v>
+        <v>13921</v>
       </c>
       <c r="AJ15" s="2">
-        <v>12208</v>
+        <v>15694</v>
+      </c>
+      <c r="AK15" s="2">
+        <v>17703</v>
+      </c>
+      <c r="AL15" s="2">
+        <v>21317</v>
+      </c>
+      <c r="AM15" s="2">
+        <v>17243</v>
+      </c>
+      <c r="AN15" s="2">
+        <v>19809</v>
       </c>
       <c r="BO15" s="2">
         <f>2031+2194+2495+3388</f>
@@ -3148,31 +3270,31 @@
       </c>
       <c r="BU15" s="2">
         <f t="shared" si="6"/>
-        <v>44374</v>
+        <v>56214</v>
       </c>
       <c r="BV15" s="2">
         <f t="shared" ref="BV15:BX15" si="12">+BU15*1.1</f>
-        <v>48811.4</v>
+        <v>61835.4</v>
       </c>
       <c r="BW15" s="2">
         <f t="shared" si="12"/>
-        <v>53692.540000000008</v>
+        <v>68018.94</v>
       </c>
       <c r="BX15" s="2">
         <f t="shared" si="12"/>
-        <v>59061.794000000016</v>
+        <v>74820.834000000003</v>
       </c>
       <c r="BY15" s="2">
         <f t="shared" ref="BY15:CA15" si="13">+BX15*1.05</f>
-        <v>62014.88370000002</v>
+        <v>78561.875700000004</v>
       </c>
       <c r="BZ15" s="2">
         <f t="shared" si="13"/>
-        <v>65115.627885000024</v>
+        <v>82489.969485000009</v>
       </c>
       <c r="CA15" s="2">
         <f t="shared" si="13"/>
-        <v>68371.409279250031</v>
+        <v>86614.467959250018</v>
       </c>
     </row>
     <row r="16" spans="1:89" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3265,6 +3387,18 @@
       <c r="AJ16" s="2">
         <v>1499</v>
       </c>
+      <c r="AK16" s="2">
+        <v>1415</v>
+      </c>
+      <c r="AL16" s="2">
+        <v>1709</v>
+      </c>
+      <c r="AM16" s="2">
+        <v>1645</v>
+      </c>
+      <c r="AN16" s="2">
+        <v>1829</v>
+      </c>
       <c r="BP16" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3410,6 +3544,18 @@
       <c r="AJ18" s="2">
         <v>68246</v>
       </c>
+      <c r="AK18" s="2">
+        <v>74058</v>
+      </c>
+      <c r="AL18" s="2">
+        <v>89992</v>
+      </c>
+      <c r="AM18" s="2">
+        <v>71304</v>
+      </c>
+      <c r="AN18" s="2">
+        <v>77602</v>
+      </c>
       <c r="BN18" s="2">
         <v>118573</v>
       </c>
@@ -3532,6 +3678,18 @@
       </c>
       <c r="AJ19" s="2">
         <v>99456</v>
+      </c>
+      <c r="AK19" s="2">
+        <v>106111</v>
+      </c>
+      <c r="AL19" s="2">
+        <v>123394</v>
+      </c>
+      <c r="AM19" s="2">
+        <v>110215</v>
+      </c>
+      <c r="AN19" s="2">
+        <v>123004</v>
       </c>
       <c r="BN19" s="2">
         <v>59293</v>
@@ -3684,17 +3842,29 @@
         <v>167702</v>
       </c>
       <c r="AK20" s="6">
-        <f>+AG20*1.1</f>
-        <v>174764.7</v>
+        <f>+AK18+AK19</f>
+        <v>180169</v>
       </c>
       <c r="AL20" s="6">
-        <f>+AH20*1.1</f>
-        <v>206571.2</v>
-      </c>
-      <c r="AM20" s="6"/>
-      <c r="AN20" s="6"/>
-      <c r="AO20" s="6"/>
-      <c r="AP20" s="6"/>
+        <f>+AL18+AL19</f>
+        <v>213386</v>
+      </c>
+      <c r="AM20" s="6">
+        <f>+AM18+AM19</f>
+        <v>181519</v>
+      </c>
+      <c r="AN20" s="6">
+        <f>+AN19+AN18</f>
+        <v>200606</v>
+      </c>
+      <c r="AO20" s="6">
+        <f>+AK20*1.13</f>
+        <v>203590.96999999997</v>
+      </c>
+      <c r="AP20" s="6">
+        <f>+AL20*1.13</f>
+        <v>241126.17999999996</v>
+      </c>
       <c r="AR20" s="5">
         <v>0.51100000000000001</v>
       </c>
@@ -3798,27 +3968,27 @@
       </c>
       <c r="BV20" s="5">
         <f t="shared" ref="BV20:CA20" si="28">SUM(BV9:BV16)</f>
-        <v>683954.35000000009</v>
+        <v>690677.55</v>
       </c>
       <c r="BW20" s="5">
         <f t="shared" si="28"/>
-        <v>741984.67749999999</v>
+        <v>750052.51750000007</v>
       </c>
       <c r="BX20" s="5">
         <f t="shared" si="28"/>
-        <v>807129.80937500019</v>
+        <v>816811.21737500012</v>
       </c>
       <c r="BY20" s="5">
         <f t="shared" si="28"/>
-        <v>865054.55904375017</v>
+        <v>876188.17824375012</v>
       </c>
       <c r="BZ20" s="5">
         <f t="shared" si="28"/>
-        <v>918409.03603593772</v>
+        <v>930656.01715593762</v>
       </c>
       <c r="CA20" s="5">
         <f t="shared" si="28"/>
-        <v>975441.41178173455</v>
+        <v>988913.09101373458</v>
       </c>
     </row>
     <row r="21" spans="2:141" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3913,6 +4083,18 @@
       <c r="AJ21" s="2">
         <v>80809</v>
       </c>
+      <c r="AK21" s="2">
+        <v>88670</v>
+      </c>
+      <c r="AL21" s="2">
+        <v>109959</v>
+      </c>
+      <c r="AM21" s="2">
+        <v>87463</v>
+      </c>
+      <c r="AN21" s="2">
+        <v>95778</v>
+      </c>
       <c r="AX21" s="2">
         <v>2323.875</v>
       </c>
@@ -3963,27 +4145,27 @@
       </c>
       <c r="BV21" s="4">
         <f t="shared" si="29"/>
-        <v>441888.86000000004</v>
+        <v>446595.10000000003</v>
       </c>
       <c r="BW21" s="4">
         <f t="shared" si="29"/>
-        <v>476793.49200000003</v>
+        <v>482440.98000000004</v>
       </c>
       <c r="BX21" s="4">
         <f t="shared" si="29"/>
-        <v>516005.39340000012</v>
+        <v>522782.37900000013</v>
       </c>
       <c r="BY21" s="4">
         <f t="shared" si="29"/>
-        <v>554103.44451000006</v>
+        <v>561896.97795000009</v>
       </c>
       <c r="BZ21" s="4">
         <f t="shared" si="29"/>
-        <v>588879.84106350003</v>
+        <v>597452.72784750001</v>
       </c>
       <c r="CA21" s="4">
         <f t="shared" si="29"/>
-        <v>626102.17987747514</v>
+        <v>635532.35533987521</v>
       </c>
     </row>
     <row r="22" spans="2:141" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4077,6 +4259,18 @@
       </c>
       <c r="AJ22" s="2">
         <v>25976</v>
+      </c>
+      <c r="AK22" s="2">
+        <v>27679</v>
+      </c>
+      <c r="AL22" s="2">
+        <v>30826</v>
+      </c>
+      <c r="AM22" s="2">
+        <v>27289</v>
+      </c>
+      <c r="AN22" s="2">
+        <v>29633</v>
       </c>
       <c r="AX22" s="2">
         <v>798.55799999999999</v>
@@ -4270,13 +4464,29 @@
         <f>AJ20-AJ21-AJ22</f>
         <v>60917</v>
       </c>
-      <c r="AK23" s="2">
-        <f t="shared" ref="AK23:AL23" si="38">+AK20*0.34</f>
-        <v>59419.998000000007</v>
+      <c r="AK23" s="4">
+        <f>AK20-AK21-AK22</f>
+        <v>63820</v>
       </c>
       <c r="AL23" s="2">
+        <f>+AL20-AL21-AL22</f>
+        <v>72601</v>
+      </c>
+      <c r="AM23" s="2">
+        <f>+AM20-AM21-AM22</f>
+        <v>66767</v>
+      </c>
+      <c r="AN23" s="2">
+        <f>+AN20-AN21-AN22</f>
+        <v>75195</v>
+      </c>
+      <c r="AO23" s="2">
+        <f t="shared" ref="AK23:AP23" si="38">+AO20*0.34</f>
+        <v>69220.929799999998</v>
+      </c>
+      <c r="AP23" s="2">
         <f t="shared" si="38"/>
-        <v>70234.208000000013</v>
+        <v>81982.901199999993</v>
       </c>
       <c r="AX23" s="2">
         <f>AX20-AX21-AX22</f>
@@ -4336,27 +4546,27 @@
       </c>
       <c r="BV23" s="4">
         <f t="shared" si="41"/>
-        <v>199732.11500000005</v>
+        <v>201749.07500000001</v>
       </c>
       <c r="BW23" s="4">
         <f t="shared" si="41"/>
-        <v>220741.14174999995</v>
+        <v>223161.49375000002</v>
       </c>
       <c r="BX23" s="4">
         <f t="shared" si="41"/>
-        <v>244451.87003750005</v>
+        <v>247356.29243749997</v>
       </c>
       <c r="BY23" s="4">
         <f t="shared" si="41"/>
-        <v>261944.94129937509</v>
+        <v>265285.02705937502</v>
       </c>
       <c r="BZ23" s="4">
         <f t="shared" si="41"/>
-        <v>278072.71307634393</v>
+        <v>281746.80741234386</v>
       </c>
       <c r="CA23" s="4">
         <f t="shared" si="41"/>
-        <v>295309.92591336096</v>
+        <v>299351.42968296091</v>
       </c>
     </row>
     <row r="24" spans="2:141" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4452,6 +4662,18 @@
       <c r="AJ24" s="2">
         <v>27166</v>
       </c>
+      <c r="AK24" s="2">
+        <v>28962</v>
+      </c>
+      <c r="AL24" s="2">
+        <v>29399</v>
+      </c>
+      <c r="AM24" s="2">
+        <v>29567</v>
+      </c>
+      <c r="AN24" s="2">
+        <v>33158</v>
+      </c>
       <c r="AX24" s="2">
         <v>241.16499999999999</v>
       </c>
@@ -4618,6 +4840,18 @@
       <c r="AJ25" s="2">
         <v>11416</v>
       </c>
+      <c r="AK25" s="2">
+        <v>11686</v>
+      </c>
+      <c r="AL25" s="2">
+        <v>14264</v>
+      </c>
+      <c r="AM25" s="2">
+        <v>10314</v>
+      </c>
+      <c r="AN25" s="2">
+        <v>11698</v>
+      </c>
       <c r="AX25" s="2">
         <v>138.28299999999999</v>
       </c>
@@ -4784,6 +5018,18 @@
       </c>
       <c r="AJ26" s="2">
         <v>2965</v>
+      </c>
+      <c r="AK26" s="2">
+        <v>2875</v>
+      </c>
+      <c r="AL26" s="2">
+        <v>2704</v>
+      </c>
+      <c r="AM26" s="2">
+        <v>2587</v>
+      </c>
+      <c r="AN26" s="2">
+        <v>2788</v>
       </c>
       <c r="AX26" s="2">
         <v>89.861999999999995</v>
@@ -4979,16 +5225,28 @@
       </c>
       <c r="AK27" s="4">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>43523</v>
       </c>
       <c r="AL27" s="4">
         <f t="shared" si="52"/>
+        <v>46367</v>
+      </c>
+      <c r="AM27" s="4">
+        <f t="shared" ref="AM27:AP27" si="53">SUM(AM24:AM26)</f>
+        <v>42468</v>
+      </c>
+      <c r="AN27" s="4">
+        <f>SUM(AN24:AN26)</f>
+        <v>47644</v>
+      </c>
+      <c r="AO27" s="4">
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
-      <c r="AM27" s="4"/>
-      <c r="AN27" s="4"/>
-      <c r="AO27" s="4"/>
-      <c r="AP27" s="4"/>
+      <c r="AP27" s="4">
+        <f t="shared" si="53"/>
+        <v>0</v>
+      </c>
       <c r="AX27" s="2">
         <f>AX26+AX25+AX24</f>
         <v>469.30999999999995</v>
@@ -5002,71 +5260,71 @@
         <v>418.89800000000002</v>
       </c>
       <c r="BK27" s="4">
-        <f t="shared" ref="BK27:BM27" si="53">SUM(BK24:BK26)</f>
+        <f t="shared" ref="BK27:BM27" si="54">SUM(BK24:BK26)</f>
         <v>15159</v>
       </c>
       <c r="BL27" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>19541</v>
       </c>
       <c r="BM27" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>25750</v>
       </c>
       <c r="BN27" s="4">
-        <f t="shared" ref="BN27" si="54">SUM(BN24:BN26)</f>
+        <f t="shared" ref="BN27" si="55">SUM(BN24:BN26)</f>
         <v>36363</v>
       </c>
       <c r="BO27" s="4">
-        <f t="shared" ref="BO27:BP27" si="55">SUM(BO24:BO26)</f>
+        <f t="shared" ref="BO27:BP27" si="56">SUM(BO24:BO26)</f>
         <v>46987</v>
       </c>
       <c r="BP27" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>60014</v>
       </c>
       <c r="BQ27" s="4">
-        <f t="shared" ref="BQ27:BR27" si="56">SUM(BQ24:BQ26)</f>
+        <f t="shared" ref="BQ27:BR27" si="57">SUM(BQ24:BQ26)</f>
         <v>71416</v>
       </c>
       <c r="BR27" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>97426</v>
       </c>
       <c r="BS27" s="4">
-        <f t="shared" ref="BS27:BT27" si="57">SUM(BS24:BS26)</f>
+        <f t="shared" ref="BS27:BT27" si="58">SUM(BS24:BS26)</f>
         <v>127342</v>
       </c>
       <c r="BT27" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>141808</v>
       </c>
       <c r="BU27" s="4">
-        <f t="shared" ref="BU27:CA27" si="58">SUM(BU24:BU26)</f>
+        <f t="shared" ref="BU27:CA27" si="59">SUM(BU24:BU26)</f>
         <v>146062.24000000002</v>
       </c>
       <c r="BV27" s="4">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>150444.10720000003</v>
       </c>
       <c r="BW27" s="4">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>154957.43041600002</v>
       </c>
       <c r="BX27" s="4">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>159606.15332848002</v>
       </c>
       <c r="BY27" s="4">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>164394.33792833443</v>
       </c>
       <c r="BZ27" s="4">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>169326.16806618447</v>
       </c>
       <c r="CA27" s="4">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>174405.95310816998</v>
       </c>
     </row>
@@ -5082,7 +5340,7 @@
       <c r="H28" s="4"/>
       <c r="I28" s="4"/>
       <c r="J28" s="4">
-        <f t="shared" ref="J28" si="59">J23-J27</f>
+        <f t="shared" ref="J28" si="60">J23-J27</f>
         <v>3872</v>
       </c>
       <c r="K28" s="4">
@@ -5090,7 +5348,7 @@
         <v>4415</v>
       </c>
       <c r="L28" s="4">
-        <f t="shared" ref="L28" si="60">L23-L27</f>
+        <f t="shared" ref="L28" si="61">L23-L27</f>
         <v>3170</v>
       </c>
       <c r="M28" s="4">
@@ -5098,15 +5356,15 @@
         <v>3212</v>
       </c>
       <c r="N28" s="4">
-        <f t="shared" ref="N28" si="61">N23-N27</f>
+        <f t="shared" ref="N28" si="62">N23-N27</f>
         <v>3944</v>
       </c>
       <c r="O28" s="4">
-        <f t="shared" ref="O28" si="62">O23-O27</f>
+        <f t="shared" ref="O28" si="63">O23-O27</f>
         <v>4059</v>
       </c>
       <c r="P28" s="4">
-        <f t="shared" ref="P28" si="63">P23-P27</f>
+        <f t="shared" ref="P28" si="64">P23-P27</f>
         <v>6133</v>
       </c>
       <c r="Q28" s="4">
@@ -5114,7 +5372,7 @@
         <v>6256</v>
       </c>
       <c r="R28" s="4">
-        <f t="shared" ref="R28" si="64">R23-R27</f>
+        <f t="shared" ref="R28" si="65">R23-R27</f>
         <v>6377</v>
       </c>
       <c r="S28" s="4">
@@ -5122,23 +5380,23 @@
         <v>8903</v>
       </c>
       <c r="T28" s="4">
-        <f t="shared" ref="T28:W28" si="65">T23-T27</f>
+        <f t="shared" ref="T28:W28" si="66">T23-T27</f>
         <v>7713</v>
       </c>
       <c r="U28" s="4">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>4841</v>
       </c>
       <c r="V28" s="4">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>3484</v>
       </c>
       <c r="W28" s="4">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>3918</v>
       </c>
       <c r="X28" s="4">
-        <f t="shared" ref="X28:AE28" si="66">X23-X27</f>
+        <f t="shared" ref="X28:AE28" si="67">X23-X27</f>
         <v>3407</v>
       </c>
       <c r="Y28" s="4">
@@ -5146,7 +5404,7 @@
         <v>2690</v>
       </c>
       <c r="Z28" s="4">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>3496</v>
       </c>
       <c r="AA28" s="4">
@@ -5154,7 +5412,7 @@
         <v>4997</v>
       </c>
       <c r="AB28" s="4">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>7827</v>
       </c>
       <c r="AC28" s="4">
@@ -5162,45 +5420,57 @@
         <v>11432</v>
       </c>
       <c r="AD28" s="4">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>13363</v>
       </c>
       <c r="AE28" s="4">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>15535</v>
       </c>
       <c r="AF28" s="4">
-        <f t="shared" ref="AF28:AL28" si="67">AF23-AF27</f>
+        <f t="shared" ref="AF28:AL28" si="68">AF23-AF27</f>
         <v>14673</v>
       </c>
       <c r="AG28" s="4">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>15258</v>
       </c>
       <c r="AH28" s="4">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>21379</v>
       </c>
       <c r="AI28" s="4">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>18972.04</v>
       </c>
       <c r="AJ28" s="4">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>19370</v>
       </c>
       <c r="AK28" s="4">
-        <f t="shared" si="67"/>
-        <v>59419.998000000007</v>
+        <f t="shared" si="68"/>
+        <v>20297</v>
       </c>
       <c r="AL28" s="4">
-        <f t="shared" si="67"/>
-        <v>70234.208000000013</v>
-      </c>
-      <c r="AM28" s="4"/>
-      <c r="AN28" s="4"/>
-      <c r="AO28" s="4"/>
-      <c r="AP28" s="4"/>
+        <f t="shared" si="68"/>
+        <v>26234</v>
+      </c>
+      <c r="AM28" s="4">
+        <f t="shared" ref="AM28:AP28" si="69">AM23-AM27</f>
+        <v>24299</v>
+      </c>
+      <c r="AN28" s="4">
+        <f>AN23-AN27</f>
+        <v>27551</v>
+      </c>
+      <c r="AO28" s="4">
+        <f t="shared" si="69"/>
+        <v>69220.929799999998</v>
+      </c>
+      <c r="AP28" s="4">
+        <f t="shared" si="69"/>
+        <v>81982.901199999993</v>
+      </c>
       <c r="AX28" s="2">
         <f>AX23-AX27</f>
         <v>-469.30999999999995</v>
@@ -5214,72 +5484,72 @@
         <v>361.23799999999972</v>
       </c>
       <c r="BK28" s="4">
-        <f t="shared" ref="BK28:BM28" si="68">BK23-BK27</f>
+        <f t="shared" ref="BK28:BM28" si="70">BK23-BK27</f>
         <v>311</v>
       </c>
       <c r="BL28" s="4">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>2404</v>
       </c>
       <c r="BM28" s="4">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>4353</v>
       </c>
       <c r="BN28" s="4">
-        <f t="shared" ref="BN28" si="69">BN23-BN27</f>
+        <f t="shared" ref="BN28" si="71">BN23-BN27</f>
         <v>4320</v>
       </c>
       <c r="BO28" s="4">
-        <f t="shared" ref="BO28:BP28" si="70">BO23-BO27</f>
+        <f t="shared" ref="BO28:BP28" si="72">BO23-BO27</f>
         <v>12717</v>
       </c>
       <c r="BP28" s="4">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v>14741</v>
       </c>
       <c r="BQ28" s="4">
-        <f t="shared" ref="BQ28:BR28" si="71">BQ23-BQ27</f>
+        <f t="shared" ref="BQ28:BR28" si="73">BQ23-BQ27</f>
         <v>22825</v>
       </c>
       <c r="BR28" s="4">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>24941</v>
       </c>
       <c r="BS28" s="4">
-        <f t="shared" ref="BS28:BT28" si="72">BS23-BS27</f>
+        <f t="shared" ref="BS28:BT28" si="74">BS23-BS27</f>
         <v>13511</v>
       </c>
       <c r="BT28" s="4">
-        <f t="shared" si="72"/>
+        <f t="shared" si="74"/>
         <v>37619</v>
       </c>
       <c r="BU28" s="4">
-        <f t="shared" ref="BU28:CA28" si="73">BU23-BU27</f>
+        <f t="shared" ref="BU28:CA28" si="75">BU23-BU27</f>
         <v>36778.059999999969</v>
       </c>
       <c r="BV28" s="4">
-        <f t="shared" si="73"/>
-        <v>49288.007800000021</v>
+        <f t="shared" si="75"/>
+        <v>51304.967799999984</v>
       </c>
       <c r="BW28" s="4">
-        <f t="shared" si="73"/>
-        <v>65783.711333999934</v>
+        <f t="shared" si="75"/>
+        <v>68204.063334000006</v>
       </c>
       <c r="BX28" s="4">
-        <f t="shared" si="73"/>
-        <v>84845.716709020024</v>
+        <f t="shared" si="75"/>
+        <v>87750.139109019947</v>
       </c>
       <c r="BY28" s="4">
-        <f t="shared" si="73"/>
-        <v>97550.603371040663</v>
+        <f t="shared" si="75"/>
+        <v>100890.68913104059</v>
       </c>
       <c r="BZ28" s="4">
-        <f t="shared" si="73"/>
-        <v>108746.54501015946</v>
+        <f t="shared" si="75"/>
+        <v>112420.63934615938</v>
       </c>
       <c r="CA28" s="4">
-        <f t="shared" si="73"/>
-        <v>120903.97280519098</v>
+        <f t="shared" si="75"/>
+        <v>124945.47657479093</v>
       </c>
     </row>
     <row r="29" spans="2:141" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5397,6 +5667,22 @@
         <f>-199+1085-516+1117</f>
         <v>1487</v>
       </c>
+      <c r="AK29" s="2">
+        <f>1100-538</f>
+        <v>562</v>
+      </c>
+      <c r="AL29" s="2">
+        <f>-679+1130</f>
+        <v>451</v>
+      </c>
+      <c r="AM29" s="2">
+        <f>-477+1135-800</f>
+        <v>-142</v>
+      </c>
+      <c r="AN29" s="2">
+        <f>1295-1314</f>
+        <v>-19</v>
+      </c>
       <c r="AX29" s="2">
         <f>29.103-139.232</f>
         <v>-110.12899999999999</v>
@@ -5454,28 +5740,28 @@
         <v>284.66000000000003</v>
       </c>
       <c r="BV29" s="2">
-        <f t="shared" ref="BV29:CA29" si="74">+BU47*$CD$46</f>
+        <f t="shared" ref="BV29:CA29" si="76">+BU47*$CD$46</f>
         <v>485.79</v>
       </c>
       <c r="BW29" s="2">
-        <f t="shared" si="74"/>
-        <v>908.86728130000017</v>
+        <f t="shared" si="76"/>
+        <v>926.01144129999989</v>
       </c>
       <c r="BX29" s="2">
-        <f t="shared" si="74"/>
-        <v>1475.7541995300498</v>
+        <f t="shared" si="76"/>
+        <v>1513.6170768900499</v>
       </c>
       <c r="BY29" s="2">
-        <f t="shared" si="74"/>
-        <v>2209.4867022527255</v>
+        <f t="shared" si="76"/>
+        <v>2272.3590044702846</v>
       </c>
       <c r="BZ29" s="2">
-        <f t="shared" si="74"/>
-        <v>3057.4474678757192</v>
+        <f t="shared" si="76"/>
+        <v>3149.2449136221271</v>
       </c>
       <c r="CA29" s="2">
-        <f t="shared" si="74"/>
-        <v>4007.7814039390187</v>
+        <f t="shared" si="76"/>
+        <v>4131.58892983027</v>
       </c>
     </row>
     <row r="30" spans="2:141" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5490,7 +5776,7 @@
       <c r="H30" s="4"/>
       <c r="I30" s="4"/>
       <c r="J30" s="4">
-        <f t="shared" ref="J30" si="75">J28+J29</f>
+        <f t="shared" ref="J30" si="77">J28+J29</f>
         <v>3350</v>
       </c>
       <c r="K30" s="4">
@@ -5498,7 +5784,7 @@
         <v>4401</v>
       </c>
       <c r="L30" s="4">
-        <f t="shared" ref="L30" si="76">L28+L29</f>
+        <f t="shared" ref="L30" si="78">L28+L29</f>
         <v>2889</v>
       </c>
       <c r="M30" s="4">
@@ -5506,15 +5792,15 @@
         <v>2632</v>
       </c>
       <c r="N30" s="4">
-        <f t="shared" ref="N30" si="77">N28+N29</f>
+        <f t="shared" ref="N30" si="79">N28+N29</f>
         <v>4053</v>
       </c>
       <c r="O30" s="4">
-        <f t="shared" ref="O30" si="78">O28+O29</f>
+        <f t="shared" ref="O30" si="80">O28+O29</f>
         <v>3383</v>
       </c>
       <c r="P30" s="4">
-        <f t="shared" ref="P30" si="79">P28+P29</f>
+        <f t="shared" ref="P30" si="81">P28+P29</f>
         <v>6221</v>
       </c>
       <c r="Q30" s="4">
@@ -5522,7 +5808,7 @@
         <v>6809</v>
       </c>
       <c r="R30" s="4">
-        <f t="shared" ref="R30" si="80">R28+R29</f>
+        <f t="shared" ref="R30" si="82">R28+R29</f>
         <v>7765</v>
       </c>
       <c r="S30" s="4">
@@ -5530,39 +5816,39 @@
         <v>10268</v>
       </c>
       <c r="T30" s="4">
-        <f t="shared" ref="T30:AL30" si="81">T28+T29</f>
+        <f t="shared" ref="T30:AL30" si="83">T28+T29</f>
         <v>8634</v>
       </c>
       <c r="U30" s="4">
-        <f t="shared" si="81"/>
+        <f t="shared" si="83"/>
         <v>4315</v>
       </c>
       <c r="V30" s="4">
-        <f t="shared" si="81"/>
+        <f t="shared" si="83"/>
         <v>14934</v>
       </c>
       <c r="W30" s="4">
-        <f t="shared" si="81"/>
+        <f t="shared" si="83"/>
         <v>-5265</v>
       </c>
       <c r="X30" s="4">
-        <f t="shared" si="81"/>
+        <f t="shared" si="83"/>
         <v>2982</v>
       </c>
       <c r="Y30" s="4">
-        <f t="shared" si="81"/>
+        <f t="shared" si="83"/>
         <v>2944</v>
       </c>
       <c r="Z30" s="4">
-        <f t="shared" si="81"/>
+        <f t="shared" si="83"/>
         <v>3247</v>
       </c>
       <c r="AA30" s="4">
-        <f t="shared" si="81"/>
+        <f t="shared" si="83"/>
         <v>4119</v>
       </c>
       <c r="AB30" s="4">
-        <f t="shared" si="81"/>
+        <f t="shared" si="83"/>
         <v>7563</v>
       </c>
       <c r="AC30" s="4">
@@ -5570,45 +5856,57 @@
         <v>12189</v>
       </c>
       <c r="AD30" s="4">
-        <f t="shared" si="81"/>
+        <f t="shared" si="83"/>
         <v>13686</v>
       </c>
       <c r="AE30" s="4">
-        <f t="shared" si="81"/>
+        <f t="shared" si="83"/>
         <v>12983</v>
       </c>
       <c r="AF30" s="4">
-        <f t="shared" si="81"/>
+        <f t="shared" si="83"/>
         <v>15246</v>
       </c>
       <c r="AG30" s="4">
-        <f t="shared" si="81"/>
+        <f t="shared" si="83"/>
         <v>15649</v>
       </c>
       <c r="AH30" s="4">
-        <f t="shared" si="81"/>
+        <f t="shared" si="83"/>
         <v>22349</v>
       </c>
       <c r="AI30" s="4">
-        <f t="shared" si="81"/>
+        <f t="shared" si="83"/>
         <v>18972.04</v>
       </c>
       <c r="AJ30" s="4">
-        <f t="shared" si="81"/>
+        <f t="shared" si="83"/>
         <v>20857</v>
       </c>
       <c r="AK30" s="4">
-        <f t="shared" si="81"/>
-        <v>59419.998000000007</v>
+        <f t="shared" si="83"/>
+        <v>20859</v>
       </c>
       <c r="AL30" s="4">
-        <f t="shared" si="81"/>
-        <v>70234.208000000013</v>
-      </c>
-      <c r="AM30" s="4"/>
-      <c r="AN30" s="4"/>
-      <c r="AO30" s="4"/>
-      <c r="AP30" s="4"/>
+        <f t="shared" si="83"/>
+        <v>26685</v>
+      </c>
+      <c r="AM30" s="4">
+        <f t="shared" ref="AM30:AP30" si="84">AM28+AM29</f>
+        <v>24157</v>
+      </c>
+      <c r="AN30" s="4">
+        <f t="shared" si="84"/>
+        <v>27532</v>
+      </c>
+      <c r="AO30" s="4">
+        <f t="shared" si="84"/>
+        <v>69220.929799999998</v>
+      </c>
+      <c r="AP30" s="4">
+        <f t="shared" si="84"/>
+        <v>81982.901199999993</v>
+      </c>
       <c r="AX30" s="2">
         <f>AX28+AX29</f>
         <v>-579.43899999999996</v>
@@ -5622,72 +5920,72 @@
         <v>253.21399999999971</v>
       </c>
       <c r="BK30" s="4">
-        <f t="shared" ref="BK30:BM30" si="82">BK28+BK29</f>
+        <f t="shared" ref="BK30:BM30" si="85">BK28+BK29</f>
         <v>-111</v>
       </c>
       <c r="BL30" s="4">
-        <f t="shared" si="82"/>
+        <f t="shared" si="85"/>
         <v>1568</v>
       </c>
       <c r="BM30" s="4">
-        <f t="shared" si="82"/>
+        <f t="shared" si="85"/>
         <v>3892</v>
       </c>
       <c r="BN30" s="4">
-        <f t="shared" ref="BN30" si="83">BN28+BN29</f>
+        <f t="shared" ref="BN30" si="86">BN28+BN29</f>
         <v>3806</v>
       </c>
       <c r="BO30" s="4">
-        <f t="shared" ref="BO30:BP30" si="84">BO28+BO29</f>
+        <f t="shared" ref="BO30:BP30" si="87">BO28+BO29</f>
         <v>11261</v>
       </c>
       <c r="BP30" s="4">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>13975</v>
       </c>
       <c r="BQ30" s="4">
-        <f t="shared" ref="BQ30:CA30" si="85">BQ28+BQ29</f>
+        <f t="shared" ref="BQ30:CA30" si="88">BQ28+BQ29</f>
         <v>24178</v>
       </c>
       <c r="BR30" s="4">
-        <f t="shared" si="85"/>
+        <f t="shared" si="88"/>
         <v>38151</v>
       </c>
       <c r="BS30" s="4">
-        <f t="shared" si="85"/>
+        <f t="shared" si="88"/>
         <v>3908</v>
       </c>
       <c r="BT30" s="4">
-        <f t="shared" si="85"/>
+        <f t="shared" si="88"/>
         <v>37557</v>
       </c>
       <c r="BU30" s="4">
-        <f t="shared" si="85"/>
+        <f t="shared" si="88"/>
         <v>37062.719999999972</v>
       </c>
       <c r="BV30" s="4">
-        <f t="shared" si="85"/>
-        <v>49773.797800000022</v>
+        <f t="shared" si="88"/>
+        <v>51790.757799999985</v>
       </c>
       <c r="BW30" s="4">
-        <f t="shared" si="85"/>
-        <v>66692.578615299935</v>
+        <f t="shared" si="88"/>
+        <v>69130.074775300003</v>
       </c>
       <c r="BX30" s="4">
-        <f t="shared" si="85"/>
-        <v>86321.47090855008</v>
+        <f t="shared" si="88"/>
+        <v>89263.756185909995</v>
       </c>
       <c r="BY30" s="4">
-        <f t="shared" si="85"/>
-        <v>99760.090073293395</v>
+        <f t="shared" si="88"/>
+        <v>103163.04813551088</v>
       </c>
       <c r="BZ30" s="4">
-        <f t="shared" si="85"/>
-        <v>111803.99247803519</v>
+        <f t="shared" si="88"/>
+        <v>115569.88425978151</v>
       </c>
       <c r="CA30" s="4">
-        <f t="shared" si="85"/>
-        <v>124911.75420913</v>
+        <f t="shared" si="88"/>
+        <v>129077.06550462119</v>
       </c>
     </row>
     <row r="31" spans="2:141" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5805,6 +6103,18 @@
         <f>2678+15</f>
         <v>2693</v>
       </c>
+      <c r="AK31" s="2">
+        <v>6910</v>
+      </c>
+      <c r="AL31" s="2">
+        <v>4946</v>
+      </c>
+      <c r="AM31" s="2">
+        <v>9560</v>
+      </c>
+      <c r="AN31" s="2">
+        <v>0</v>
+      </c>
       <c r="AX31" s="2">
         <v>0</v>
       </c>
@@ -5859,28 +6169,28 @@
         <v>5559.4079999999958</v>
       </c>
       <c r="BV31" s="2">
-        <f t="shared" ref="BV31:CA31" si="86">+BV30*0.15</f>
-        <v>7466.0696700000026</v>
+        <f t="shared" ref="BV31:CA31" si="89">+BV30*0.15</f>
+        <v>7768.613669999997</v>
       </c>
       <c r="BW31" s="2">
-        <f t="shared" si="86"/>
-        <v>10003.88679229499</v>
+        <f t="shared" si="89"/>
+        <v>10369.511216295001</v>
       </c>
       <c r="BX31" s="2">
-        <f t="shared" si="86"/>
-        <v>12948.220636282511</v>
+        <f t="shared" si="89"/>
+        <v>13389.563427886498</v>
       </c>
       <c r="BY31" s="2">
-        <f t="shared" si="86"/>
-        <v>14964.013510994009</v>
+        <f t="shared" si="89"/>
+        <v>15474.457220326631</v>
       </c>
       <c r="BZ31" s="2">
-        <f t="shared" si="86"/>
-        <v>16770.598871705279</v>
+        <f t="shared" si="89"/>
+        <v>17335.482638967227</v>
       </c>
       <c r="CA31" s="2">
-        <f t="shared" si="86"/>
-        <v>18736.763131369498</v>
+        <f t="shared" si="89"/>
+        <v>19361.559825693177</v>
       </c>
     </row>
     <row r="32" spans="2:141" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5895,7 +6205,7 @@
       <c r="H32" s="4"/>
       <c r="I32" s="4"/>
       <c r="J32" s="4">
-        <f t="shared" ref="J32" si="87">J30-J31</f>
+        <f t="shared" ref="J32" si="90">J30-J31</f>
         <v>3027</v>
       </c>
       <c r="K32" s="4">
@@ -5903,7 +6213,7 @@
         <v>3561</v>
       </c>
       <c r="L32" s="4">
-        <f t="shared" ref="L32" si="88">L30-L31</f>
+        <f t="shared" ref="L32" si="91">L30-L31</f>
         <v>2625</v>
       </c>
       <c r="M32" s="4">
@@ -5911,15 +6221,15 @@
         <v>2134</v>
       </c>
       <c r="N32" s="4">
-        <f t="shared" ref="N32" si="89">N30-N31</f>
+        <f t="shared" ref="N32" si="92">N30-N31</f>
         <v>3268</v>
       </c>
       <c r="O32" s="4">
-        <f t="shared" ref="O32" si="90">O30-O31</f>
+        <f t="shared" ref="O32" si="93">O30-O31</f>
         <v>2535</v>
       </c>
       <c r="P32" s="4">
-        <f t="shared" ref="P32" si="91">P30-P31</f>
+        <f t="shared" ref="P32" si="94">P30-P31</f>
         <v>5243</v>
       </c>
       <c r="Q32" s="4">
@@ -5927,7 +6237,7 @@
         <v>6331</v>
       </c>
       <c r="R32" s="4">
-        <f t="shared" ref="R32" si="92">R30-R31</f>
+        <f t="shared" ref="R32" si="95">R30-R31</f>
         <v>7222</v>
       </c>
       <c r="S32" s="4">
@@ -5935,85 +6245,97 @@
         <v>8107</v>
       </c>
       <c r="T32" s="4">
-        <f t="shared" ref="T32:AL32" si="93">T30-T31</f>
+        <f t="shared" ref="T32:AL32" si="96">T30-T31</f>
         <v>7778</v>
       </c>
       <c r="U32" s="4">
-        <f t="shared" si="93"/>
+        <f t="shared" si="96"/>
         <v>3156</v>
       </c>
       <c r="V32" s="4">
-        <f t="shared" si="93"/>
+        <f t="shared" si="96"/>
         <v>14323</v>
       </c>
       <c r="W32" s="4">
-        <f t="shared" si="93"/>
+        <f t="shared" si="96"/>
         <v>-3844</v>
       </c>
       <c r="X32" s="4">
-        <f t="shared" si="93"/>
+        <f t="shared" si="96"/>
         <v>2982</v>
       </c>
       <c r="Y32" s="4">
-        <f t="shared" si="93"/>
+        <f t="shared" si="96"/>
         <v>2872</v>
       </c>
       <c r="Z32" s="4">
-        <f t="shared" si="93"/>
+        <f t="shared" si="96"/>
         <v>3247</v>
       </c>
       <c r="AA32" s="4">
-        <f t="shared" si="93"/>
+        <f t="shared" si="96"/>
         <v>3172</v>
       </c>
       <c r="AB32" s="4">
-        <f t="shared" si="93"/>
+        <f t="shared" si="96"/>
         <v>6750</v>
       </c>
       <c r="AC32" s="4">
-        <f t="shared" si="93"/>
+        <f t="shared" si="96"/>
         <v>9879</v>
       </c>
       <c r="AD32" s="4">
-        <f t="shared" si="93"/>
+        <f t="shared" si="96"/>
         <v>10624</v>
       </c>
       <c r="AE32" s="4">
-        <f t="shared" si="93"/>
+        <f t="shared" si="96"/>
         <v>10431</v>
       </c>
       <c r="AF32" s="4">
-        <f t="shared" si="93"/>
+        <f t="shared" si="96"/>
         <v>13486</v>
       </c>
       <c r="AG32" s="4">
-        <f t="shared" si="93"/>
+        <f t="shared" si="96"/>
         <v>12940</v>
       </c>
       <c r="AH32" s="4">
-        <f t="shared" si="93"/>
+        <f t="shared" si="96"/>
         <v>20024</v>
       </c>
       <c r="AI32" s="4">
-        <f t="shared" si="93"/>
+        <f t="shared" si="96"/>
         <v>17074.835999999999</v>
       </c>
       <c r="AJ32" s="4">
-        <f t="shared" si="93"/>
+        <f t="shared" si="96"/>
         <v>18164</v>
       </c>
       <c r="AK32" s="4">
-        <f t="shared" si="93"/>
-        <v>59419.998000000007</v>
+        <f t="shared" si="96"/>
+        <v>13949</v>
       </c>
       <c r="AL32" s="4">
-        <f t="shared" si="93"/>
-        <v>70234.208000000013</v>
-      </c>
-      <c r="AM32" s="4"/>
-      <c r="AN32" s="4"/>
-      <c r="AO32" s="4"/>
-      <c r="AP32" s="4"/>
+        <f t="shared" si="96"/>
+        <v>21739</v>
+      </c>
+      <c r="AM32" s="4">
+        <f t="shared" ref="AM32:AP32" si="97">AM30-AM31</f>
+        <v>14597</v>
+      </c>
+      <c r="AN32" s="4">
+        <f t="shared" si="97"/>
+        <v>27532</v>
+      </c>
+      <c r="AO32" s="4">
+        <f t="shared" si="97"/>
+        <v>69220.929799999998</v>
+      </c>
+      <c r="AP32" s="4">
+        <f t="shared" si="97"/>
+        <v>81982.901199999993</v>
+      </c>
       <c r="AX32" s="2">
         <f>AX30-AX31</f>
         <v>-579.43899999999996</v>
@@ -6027,320 +6349,320 @@
         <v>253.21399999999971</v>
       </c>
       <c r="BK32" s="4">
-        <f t="shared" ref="BK32:BM32" si="94">BK30-BK31</f>
+        <f t="shared" ref="BK32:BM32" si="98">BK30-BK31</f>
         <v>-241</v>
       </c>
       <c r="BL32" s="4">
-        <f t="shared" si="94"/>
+        <f t="shared" si="98"/>
         <v>596</v>
       </c>
       <c r="BM32" s="4">
-        <f t="shared" si="94"/>
+        <f t="shared" si="98"/>
         <v>2371</v>
       </c>
       <c r="BN32" s="4">
-        <f t="shared" ref="BN32" si="95">BN30-BN31</f>
+        <f t="shared" ref="BN32" si="99">BN30-BN31</f>
         <v>3033</v>
       </c>
       <c r="BO32" s="4">
-        <f t="shared" ref="BO32:BP32" si="96">BO30-BO31</f>
+        <f t="shared" ref="BO32:BP32" si="100">BO30-BO31</f>
         <v>10073</v>
       </c>
       <c r="BP32" s="4">
-        <f t="shared" si="96"/>
+        <f t="shared" si="100"/>
         <v>11588</v>
       </c>
       <c r="BQ32" s="4">
-        <f t="shared" ref="BQ32:BT32" si="97">BQ30-BQ31</f>
+        <f t="shared" ref="BQ32:BT32" si="101">BQ30-BQ31</f>
         <v>21331</v>
       </c>
       <c r="BR32" s="4">
-        <f t="shared" si="97"/>
+        <f t="shared" si="101"/>
         <v>33364</v>
       </c>
       <c r="BS32" s="4">
-        <f t="shared" si="97"/>
+        <f t="shared" si="101"/>
         <v>5257</v>
       </c>
       <c r="BT32" s="4">
-        <f t="shared" si="97"/>
+        <f t="shared" si="101"/>
         <v>30425</v>
       </c>
       <c r="BU32" s="4">
-        <f t="shared" ref="BU32:CA32" si="98">BU30-BU31</f>
+        <f t="shared" ref="BU32:CA32" si="102">BU30-BU31</f>
         <v>31503.311999999976</v>
       </c>
       <c r="BV32" s="4">
-        <f t="shared" si="98"/>
-        <v>42307.728130000018</v>
+        <f t="shared" si="102"/>
+        <v>44022.144129999986</v>
       </c>
       <c r="BW32" s="4">
-        <f t="shared" si="98"/>
-        <v>56688.691823004949</v>
+        <f t="shared" si="102"/>
+        <v>58760.563559005001</v>
       </c>
       <c r="BX32" s="4">
-        <f t="shared" si="98"/>
-        <v>73373.250272267571</v>
+        <f t="shared" si="102"/>
+        <v>75874.192758023491</v>
       </c>
       <c r="BY32" s="4">
-        <f t="shared" si="98"/>
-        <v>84796.076562299393</v>
+        <f t="shared" si="102"/>
+        <v>87688.59091518425</v>
       </c>
       <c r="BZ32" s="4">
-        <f t="shared" si="98"/>
-        <v>95033.393606329904</v>
+        <f t="shared" si="102"/>
+        <v>98234.401620814286</v>
       </c>
       <c r="CA32" s="4">
-        <f t="shared" si="98"/>
-        <v>106174.9910777605</v>
+        <f t="shared" si="102"/>
+        <v>109715.50567892802</v>
       </c>
       <c r="CB32" s="2">
         <f>+CA32*(1+$CD$47)</f>
-        <v>106174.9910777605</v>
+        <v>109715.50567892802</v>
       </c>
       <c r="CC32" s="2">
-        <f t="shared" ref="CC32:EK32" si="99">+CB32*(1+$CD$47)</f>
-        <v>106174.9910777605</v>
+        <f t="shared" ref="CC32:EK32" si="103">+CB32*(1+$CD$47)</f>
+        <v>109715.50567892802</v>
       </c>
       <c r="CD32" s="2">
-        <f t="shared" si="99"/>
-        <v>106174.9910777605</v>
+        <f t="shared" si="103"/>
+        <v>109715.50567892802</v>
       </c>
       <c r="CE32" s="2">
-        <f t="shared" si="99"/>
-        <v>106174.9910777605</v>
+        <f t="shared" si="103"/>
+        <v>109715.50567892802</v>
       </c>
       <c r="CF32" s="2">
-        <f t="shared" si="99"/>
-        <v>106174.9910777605</v>
+        <f t="shared" si="103"/>
+        <v>109715.50567892802</v>
       </c>
       <c r="CG32" s="2">
-        <f t="shared" si="99"/>
-        <v>106174.9910777605</v>
+        <f t="shared" si="103"/>
+        <v>109715.50567892802</v>
       </c>
       <c r="CH32" s="2">
-        <f t="shared" si="99"/>
-        <v>106174.9910777605</v>
+        <f t="shared" si="103"/>
+        <v>109715.50567892802</v>
       </c>
       <c r="CI32" s="2">
-        <f t="shared" si="99"/>
-        <v>106174.9910777605</v>
+        <f t="shared" si="103"/>
+        <v>109715.50567892802</v>
       </c>
       <c r="CJ32" s="2">
-        <f t="shared" si="99"/>
-        <v>106174.9910777605</v>
+        <f t="shared" si="103"/>
+        <v>109715.50567892802</v>
       </c>
       <c r="CK32" s="2">
-        <f t="shared" si="99"/>
-        <v>106174.9910777605</v>
+        <f t="shared" si="103"/>
+        <v>109715.50567892802</v>
       </c>
       <c r="CL32" s="2">
-        <f t="shared" si="99"/>
-        <v>106174.9910777605</v>
+        <f t="shared" si="103"/>
+        <v>109715.50567892802</v>
       </c>
       <c r="CM32" s="2">
-        <f t="shared" si="99"/>
-        <v>106174.9910777605</v>
+        <f t="shared" si="103"/>
+        <v>109715.50567892802</v>
       </c>
       <c r="CN32" s="2">
-        <f t="shared" si="99"/>
-        <v>106174.9910777605</v>
+        <f t="shared" si="103"/>
+        <v>109715.50567892802</v>
       </c>
       <c r="CO32" s="2">
-        <f t="shared" si="99"/>
-        <v>106174.9910777605</v>
+        <f t="shared" si="103"/>
+        <v>109715.50567892802</v>
       </c>
       <c r="CP32" s="2">
-        <f t="shared" si="99"/>
-        <v>106174.9910777605</v>
+        <f t="shared" si="103"/>
+        <v>109715.50567892802</v>
       </c>
       <c r="CQ32" s="2">
-        <f t="shared" si="99"/>
-        <v>106174.9910777605</v>
+        <f t="shared" si="103"/>
+        <v>109715.50567892802</v>
       </c>
       <c r="CR32" s="2">
-        <f t="shared" si="99"/>
-        <v>106174.9910777605</v>
+        <f t="shared" si="103"/>
+        <v>109715.50567892802</v>
       </c>
       <c r="CS32" s="2">
-        <f t="shared" si="99"/>
-        <v>106174.9910777605</v>
+        <f t="shared" si="103"/>
+        <v>109715.50567892802</v>
       </c>
       <c r="CT32" s="2">
-        <f t="shared" si="99"/>
-        <v>106174.9910777605</v>
+        <f t="shared" si="103"/>
+        <v>109715.50567892802</v>
       </c>
       <c r="CU32" s="2">
-        <f t="shared" si="99"/>
-        <v>106174.9910777605</v>
+        <f t="shared" si="103"/>
+        <v>109715.50567892802</v>
       </c>
       <c r="CV32" s="2">
-        <f t="shared" si="99"/>
-        <v>106174.9910777605</v>
+        <f t="shared" si="103"/>
+        <v>109715.50567892802</v>
       </c>
       <c r="CW32" s="2">
-        <f t="shared" si="99"/>
-        <v>106174.9910777605</v>
+        <f t="shared" si="103"/>
+        <v>109715.50567892802</v>
       </c>
       <c r="CX32" s="2">
-        <f t="shared" si="99"/>
-        <v>106174.9910777605</v>
+        <f t="shared" si="103"/>
+        <v>109715.50567892802</v>
       </c>
       <c r="CY32" s="2">
-        <f t="shared" si="99"/>
-        <v>106174.9910777605</v>
+        <f t="shared" si="103"/>
+        <v>109715.50567892802</v>
       </c>
       <c r="CZ32" s="2">
-        <f t="shared" si="99"/>
-        <v>106174.9910777605</v>
+        <f t="shared" si="103"/>
+        <v>109715.50567892802</v>
       </c>
       <c r="DA32" s="2">
-        <f t="shared" si="99"/>
-        <v>106174.9910777605</v>
+        <f t="shared" si="103"/>
+        <v>109715.50567892802</v>
       </c>
       <c r="DB32" s="2">
-        <f t="shared" si="99"/>
-        <v>106174.9910777605</v>
+        <f t="shared" si="103"/>
+        <v>109715.50567892802</v>
       </c>
       <c r="DC32" s="2">
-        <f t="shared" si="99"/>
-        <v>106174.9910777605</v>
+        <f t="shared" si="103"/>
+        <v>109715.50567892802</v>
       </c>
       <c r="DD32" s="2">
-        <f t="shared" si="99"/>
-        <v>106174.9910777605</v>
+        <f t="shared" si="103"/>
+        <v>109715.50567892802</v>
       </c>
       <c r="DE32" s="2">
-        <f t="shared" si="99"/>
-        <v>106174.9910777605</v>
+        <f t="shared" si="103"/>
+        <v>109715.50567892802</v>
       </c>
       <c r="DF32" s="2">
-        <f t="shared" si="99"/>
-        <v>106174.9910777605</v>
+        <f t="shared" si="103"/>
+        <v>109715.50567892802</v>
       </c>
       <c r="DG32" s="2">
-        <f t="shared" si="99"/>
-        <v>106174.9910777605</v>
+        <f t="shared" si="103"/>
+        <v>109715.50567892802</v>
       </c>
       <c r="DH32" s="2">
-        <f t="shared" si="99"/>
-        <v>106174.9910777605</v>
+        <f t="shared" si="103"/>
+        <v>109715.50567892802</v>
       </c>
       <c r="DI32" s="2">
-        <f t="shared" si="99"/>
-        <v>106174.9910777605</v>
+        <f t="shared" si="103"/>
+        <v>109715.50567892802</v>
       </c>
       <c r="DJ32" s="2">
-        <f t="shared" si="99"/>
-        <v>106174.9910777605</v>
+        <f t="shared" si="103"/>
+        <v>109715.50567892802</v>
       </c>
       <c r="DK32" s="2">
-        <f t="shared" si="99"/>
-        <v>106174.9910777605</v>
+        <f t="shared" si="103"/>
+        <v>109715.50567892802</v>
       </c>
       <c r="DL32" s="2">
-        <f t="shared" si="99"/>
-        <v>106174.9910777605</v>
+        <f t="shared" si="103"/>
+        <v>109715.50567892802</v>
       </c>
       <c r="DM32" s="2">
-        <f t="shared" si="99"/>
-        <v>106174.9910777605</v>
+        <f t="shared" si="103"/>
+        <v>109715.50567892802</v>
       </c>
       <c r="DN32" s="2">
-        <f t="shared" si="99"/>
-        <v>106174.9910777605</v>
+        <f t="shared" si="103"/>
+        <v>109715.50567892802</v>
       </c>
       <c r="DO32" s="2">
-        <f t="shared" si="99"/>
-        <v>106174.9910777605</v>
+        <f t="shared" si="103"/>
+        <v>109715.50567892802</v>
       </c>
       <c r="DP32" s="2">
-        <f t="shared" si="99"/>
-        <v>106174.9910777605</v>
+        <f t="shared" si="103"/>
+        <v>109715.50567892802</v>
       </c>
       <c r="DQ32" s="2">
-        <f t="shared" si="99"/>
-        <v>106174.9910777605</v>
+        <f t="shared" si="103"/>
+        <v>109715.50567892802</v>
       </c>
       <c r="DR32" s="2">
-        <f t="shared" si="99"/>
-        <v>106174.9910777605</v>
+        <f t="shared" si="103"/>
+        <v>109715.50567892802</v>
       </c>
       <c r="DS32" s="2">
-        <f t="shared" si="99"/>
-        <v>106174.9910777605</v>
+        <f t="shared" si="103"/>
+        <v>109715.50567892802</v>
       </c>
       <c r="DT32" s="2">
-        <f t="shared" si="99"/>
-        <v>106174.9910777605</v>
+        <f t="shared" si="103"/>
+        <v>109715.50567892802</v>
       </c>
       <c r="DU32" s="2">
-        <f t="shared" si="99"/>
-        <v>106174.9910777605</v>
+        <f t="shared" si="103"/>
+        <v>109715.50567892802</v>
       </c>
       <c r="DV32" s="2">
-        <f t="shared" si="99"/>
-        <v>106174.9910777605</v>
+        <f t="shared" si="103"/>
+        <v>109715.50567892802</v>
       </c>
       <c r="DW32" s="2">
-        <f t="shared" si="99"/>
-        <v>106174.9910777605</v>
+        <f t="shared" si="103"/>
+        <v>109715.50567892802</v>
       </c>
       <c r="DX32" s="2">
-        <f t="shared" si="99"/>
-        <v>106174.9910777605</v>
+        <f t="shared" si="103"/>
+        <v>109715.50567892802</v>
       </c>
       <c r="DY32" s="2">
-        <f t="shared" si="99"/>
-        <v>106174.9910777605</v>
+        <f t="shared" si="103"/>
+        <v>109715.50567892802</v>
       </c>
       <c r="DZ32" s="2">
-        <f t="shared" si="99"/>
-        <v>106174.9910777605</v>
+        <f t="shared" si="103"/>
+        <v>109715.50567892802</v>
       </c>
       <c r="EA32" s="2">
-        <f t="shared" si="99"/>
-        <v>106174.9910777605</v>
+        <f t="shared" si="103"/>
+        <v>109715.50567892802</v>
       </c>
       <c r="EB32" s="2">
-        <f t="shared" si="99"/>
-        <v>106174.9910777605</v>
+        <f t="shared" si="103"/>
+        <v>109715.50567892802</v>
       </c>
       <c r="EC32" s="2">
-        <f t="shared" si="99"/>
-        <v>106174.9910777605</v>
+        <f t="shared" si="103"/>
+        <v>109715.50567892802</v>
       </c>
       <c r="ED32" s="2">
-        <f t="shared" si="99"/>
-        <v>106174.9910777605</v>
+        <f t="shared" si="103"/>
+        <v>109715.50567892802</v>
       </c>
       <c r="EE32" s="2">
-        <f t="shared" si="99"/>
-        <v>106174.9910777605</v>
+        <f t="shared" si="103"/>
+        <v>109715.50567892802</v>
       </c>
       <c r="EF32" s="2">
-        <f t="shared" si="99"/>
-        <v>106174.9910777605</v>
+        <f t="shared" si="103"/>
+        <v>109715.50567892802</v>
       </c>
       <c r="EG32" s="2">
-        <f t="shared" si="99"/>
-        <v>106174.9910777605</v>
+        <f t="shared" si="103"/>
+        <v>109715.50567892802</v>
       </c>
       <c r="EH32" s="2">
-        <f t="shared" si="99"/>
-        <v>106174.9910777605</v>
+        <f t="shared" si="103"/>
+        <v>109715.50567892802</v>
       </c>
       <c r="EI32" s="2">
-        <f t="shared" si="99"/>
-        <v>106174.9910777605</v>
+        <f t="shared" si="103"/>
+        <v>109715.50567892802</v>
       </c>
       <c r="EJ32" s="2">
-        <f t="shared" si="99"/>
-        <v>106174.9910777605</v>
+        <f t="shared" si="103"/>
+        <v>109715.50567892802</v>
       </c>
       <c r="EK32" s="2">
-        <f t="shared" si="99"/>
-        <v>106174.9910777605</v>
+        <f t="shared" si="103"/>
+        <v>109715.50567892802</v>
       </c>
     </row>
     <row r="33" spans="2:82" x14ac:dyDescent="0.25">
@@ -6355,7 +6677,7 @@
       <c r="H33" s="7"/>
       <c r="I33" s="7"/>
       <c r="J33" s="7">
-        <f t="shared" ref="J33" si="100">J32/J34</f>
+        <f t="shared" ref="J33" si="104">J32/J34</f>
         <v>6.0419161676646711</v>
       </c>
       <c r="K33" s="7">
@@ -6363,7 +6685,7 @@
         <v>7.0936254980079685</v>
       </c>
       <c r="L33" s="7">
-        <f t="shared" ref="L33" si="101">L32/L34</f>
+        <f t="shared" ref="L33" si="105">L32/L34</f>
         <v>5.2186878727634198</v>
       </c>
       <c r="M33" s="7">
@@ -6371,15 +6693,15 @@
         <v>4.2341269841269842</v>
       </c>
       <c r="N33" s="7">
-        <f t="shared" ref="N33" si="102">N32/N34</f>
+        <f t="shared" ref="N33" si="106">N32/N34</f>
         <v>6.4712871287128717</v>
       </c>
       <c r="O33" s="7">
-        <f t="shared" ref="O33" si="103">O32/O34</f>
+        <f t="shared" ref="O33" si="107">O32/O34</f>
         <v>5.0098814229249014</v>
       </c>
       <c r="P33" s="7">
-        <f t="shared" ref="P33" si="104">P32/P34</f>
+        <f t="shared" ref="P33" si="108">P32/P34</f>
         <v>10.300589390962672</v>
       </c>
       <c r="Q33" s="7">
@@ -6387,7 +6709,7 @@
         <v>12.365234375</v>
       </c>
       <c r="R33" s="7">
-        <f t="shared" ref="R33" si="105">R32/R34</f>
+        <f t="shared" ref="R33" si="109">R32/R34</f>
         <v>14.077972709551657</v>
       </c>
       <c r="S33" s="7">
@@ -6411,69 +6733,81 @@
         <v>-7.5520628683693518</v>
       </c>
       <c r="X33" s="7">
-        <f t="shared" ref="X33:AL33" si="106">X32/X34</f>
+        <f t="shared" ref="X33:AL33" si="110">X32/X34</f>
         <v>0.29307125307125309</v>
       </c>
       <c r="Y33" s="7">
-        <f t="shared" si="106"/>
+        <f t="shared" si="110"/>
         <v>0.27799825767108705</v>
       </c>
       <c r="Z33" s="7">
-        <f t="shared" si="106"/>
+        <f t="shared" si="110"/>
         <v>0.31499805975941014</v>
       </c>
       <c r="AA33" s="7">
-        <f t="shared" si="106"/>
+        <f t="shared" si="110"/>
         <v>0.3065622885860636</v>
       </c>
       <c r="AB33" s="7">
-        <f t="shared" si="106"/>
+        <f t="shared" si="110"/>
         <v>0.64599483204134367</v>
       </c>
       <c r="AC33" s="7">
-        <f t="shared" si="106"/>
+        <f t="shared" si="110"/>
         <v>0.93568857738207989</v>
       </c>
       <c r="AD33" s="7">
-        <f t="shared" si="106"/>
+        <f t="shared" si="110"/>
         <v>1.0013195098963241</v>
       </c>
       <c r="AE33" s="7">
-        <f t="shared" si="106"/>
+        <f t="shared" si="110"/>
         <v>0.97760074976569822</v>
       </c>
       <c r="AF33" s="7">
-        <f t="shared" si="106"/>
+        <f t="shared" si="110"/>
         <v>1.2594322002241314</v>
       </c>
       <c r="AG33" s="7">
-        <f t="shared" si="106"/>
+        <f t="shared" si="110"/>
         <v>1.2054028877503493</v>
       </c>
       <c r="AH33" s="7">
-        <f t="shared" si="106"/>
+        <f t="shared" si="110"/>
         <v>1.8590660105839756</v>
       </c>
       <c r="AI33" s="7">
-        <f t="shared" si="106"/>
+        <f t="shared" si="110"/>
         <v>1.5820287223200222</v>
       </c>
       <c r="AJ33" s="7">
-        <f t="shared" si="106"/>
+        <f t="shared" si="110"/>
         <v>1.6809180085137887</v>
       </c>
       <c r="AK33" s="7">
-        <f t="shared" si="106"/>
-        <v>5.4987967795669075</v>
+        <f t="shared" si="110"/>
+        <v>1.2862148455509452</v>
       </c>
       <c r="AL33" s="7">
-        <f t="shared" si="106"/>
-        <v>6.4995565426614856</v>
-      </c>
-      <c r="AM33" s="7"/>
-      <c r="AN33" s="7"/>
-      <c r="AO33" s="7"/>
-      <c r="AP33" s="7"/>
+        <f t="shared" si="110"/>
+        <v>2.0011967228205836</v>
+      </c>
+      <c r="AM33" s="7">
+        <f t="shared" ref="AM33:AP33" si="111">AM32/AM34</f>
+        <v>1.3423763104653301</v>
+      </c>
+      <c r="AN33" s="7">
+        <f t="shared" si="111"/>
+        <v>2.5251765569109419</v>
+      </c>
+      <c r="AO33" s="7">
+        <f t="shared" si="111"/>
+        <v>6.3487966431257448</v>
+      </c>
+      <c r="AP33" s="7">
+        <f t="shared" si="111"/>
+        <v>7.5192975511327154</v>
+      </c>
       <c r="AX33" s="1">
         <f>AX32/AX34</f>
         <v>-1.5909431620681416</v>
@@ -6487,27 +6821,27 @@
         <v>0.60382208741105259</v>
       </c>
       <c r="BK33" s="7">
-        <f t="shared" ref="BK33" si="107">BK32/BK34</f>
+        <f t="shared" ref="BK33" si="112">BK32/BK34</f>
         <v>-0.52164502164502169</v>
       </c>
       <c r="BL33" s="7">
-        <f t="shared" ref="BL33" si="108">BL32/BL34</f>
+        <f t="shared" ref="BL33" si="113">BL32/BL34</f>
         <v>1.249475890985325</v>
       </c>
       <c r="BM33" s="7">
-        <f t="shared" ref="BM33" si="109">BM32/BM34</f>
+        <f t="shared" ref="BM33" si="114">BM32/BM34</f>
         <v>4.8987603305785123</v>
       </c>
       <c r="BN33" s="7">
-        <f t="shared" ref="BN33" si="110">BN32/BN34</f>
+        <f t="shared" ref="BN33" si="115">BN32/BN34</f>
         <v>6.1521298174442194</v>
       </c>
       <c r="BO33" s="7">
-        <f t="shared" ref="BO33:BP33" si="111">BO32/BO34</f>
+        <f t="shared" ref="BO33:BP33" si="116">BO32/BO34</f>
         <v>20.146000000000001</v>
       </c>
       <c r="BP33" s="7">
-        <f t="shared" si="111"/>
+        <f t="shared" si="116"/>
         <v>23.014895729890764</v>
       </c>
       <c r="BQ33" s="7">
@@ -6519,40 +6853,40 @@
         <v>6.1676679914964412</v>
       </c>
       <c r="BS33" s="7">
-        <f t="shared" ref="BS33:BT33" si="112">BS32/BS34</f>
+        <f t="shared" ref="BS33:BT33" si="117">BS32/BS34</f>
         <v>0.51665847665847664</v>
       </c>
       <c r="BT33" s="7">
-        <f t="shared" si="112"/>
+        <f t="shared" si="117"/>
         <v>2.9001048517777144</v>
       </c>
       <c r="BU33" s="7">
-        <f t="shared" ref="BU33" si="113">BU32/BU34</f>
+        <f t="shared" ref="BU33" si="118">BU32/BU34</f>
         <v>2.9384676802537055</v>
       </c>
       <c r="BV33" s="7">
-        <f t="shared" ref="BV33" si="114">BV32/BV34</f>
-        <v>3.9163850065955446</v>
+        <f t="shared" ref="BV33" si="119">BV32/BV34</f>
+        <v>4.0660534444777969</v>
       </c>
       <c r="BW33" s="7">
-        <f t="shared" ref="BW33" si="115">BW32/BW34</f>
-        <v>5.2476167478655853</v>
+        <f t="shared" ref="BW33" si="120">BW32/BW34</f>
+        <v>5.4273501797866395</v>
       </c>
       <c r="BX33" s="7">
-        <f t="shared" ref="BX33" si="116">BX32/BX34</f>
-        <v>6.79209000229271</v>
+        <f t="shared" ref="BX33" si="121">BX32/BX34</f>
+        <v>7.0080303653472642</v>
       </c>
       <c r="BY33" s="7">
-        <f t="shared" ref="BY33" si="117">BY32/BY34</f>
-        <v>7.8494898578879813</v>
+        <f t="shared" ref="BY33" si="122">BY32/BY34</f>
+        <v>8.0992533230363914</v>
       </c>
       <c r="BZ33" s="7">
-        <f t="shared" ref="BZ33" si="118">BZ32/BZ34</f>
-        <v>8.7971482822734863</v>
+        <f t="shared" ref="BZ33" si="123">BZ32/BZ34</f>
+        <v>9.0733046963136932</v>
       </c>
       <c r="CA33" s="7">
-        <f t="shared" ref="CA33" si="119">CA32/CA34</f>
-        <v>9.8285150612353789</v>
+        <f t="shared" ref="CA33" si="124">CA32/CA34</f>
+        <v>10.133743337467664</v>
       </c>
     </row>
     <row r="34" spans="2:82" x14ac:dyDescent="0.25">
@@ -6641,17 +6975,25 @@
         <v>10806</v>
       </c>
       <c r="AK34" s="2">
-        <f>+AJ34</f>
-        <v>10806</v>
+        <v>10845</v>
       </c>
       <c r="AL34" s="2">
-        <f>+AK34</f>
-        <v>10806</v>
-      </c>
-      <c r="AM34" s="2"/>
-      <c r="AN34" s="2"/>
-      <c r="AO34" s="2"/>
-      <c r="AP34" s="2"/>
+        <v>10863</v>
+      </c>
+      <c r="AM34" s="2">
+        <v>10874</v>
+      </c>
+      <c r="AN34" s="2">
+        <v>10903</v>
+      </c>
+      <c r="AO34" s="2">
+        <f t="shared" ref="AN34:AP34" si="125">+AN34</f>
+        <v>10903</v>
+      </c>
+      <c r="AP34" s="2">
+        <f t="shared" si="125"/>
+        <v>10903</v>
+      </c>
       <c r="AV34" s="2">
         <v>161.096869</v>
       </c>
@@ -6705,27 +7047,27 @@
       </c>
       <c r="BV34" s="2">
         <f>AVERAGE(AI34:AL34)</f>
-        <v>10802.75</v>
+        <v>10826.75</v>
       </c>
       <c r="BW34" s="2">
-        <f t="shared" ref="BW34:CA34" si="120">+BV34</f>
-        <v>10802.75</v>
+        <f t="shared" ref="BW34:CA34" si="126">+BV34</f>
+        <v>10826.75</v>
       </c>
       <c r="BX34" s="2">
-        <f t="shared" si="120"/>
-        <v>10802.75</v>
+        <f t="shared" si="126"/>
+        <v>10826.75</v>
       </c>
       <c r="BY34" s="2">
-        <f t="shared" si="120"/>
-        <v>10802.75</v>
+        <f t="shared" si="126"/>
+        <v>10826.75</v>
       </c>
       <c r="BZ34" s="2">
-        <f t="shared" si="120"/>
-        <v>10802.75</v>
+        <f t="shared" si="126"/>
+        <v>10826.75</v>
       </c>
       <c r="CA34" s="2">
-        <f t="shared" si="120"/>
-        <v>10802.75</v>
+        <f t="shared" si="126"/>
+        <v>10826.75</v>
       </c>
     </row>
     <row r="36" spans="2:82" s="11" customFormat="1" ht="13" x14ac:dyDescent="0.3">
@@ -6752,31 +7094,31 @@
         <v>0.26385259631490787</v>
       </c>
       <c r="P36" s="10">
-        <f t="shared" ref="P36:R36" si="121">P20/L20-1</f>
+        <f t="shared" ref="P36:R36" si="127">P20/L20-1</f>
         <v>0.40230900258658764</v>
       </c>
       <c r="Q36" s="10">
-        <f t="shared" si="121"/>
+        <f t="shared" si="127"/>
         <v>0.37387290836084075</v>
       </c>
       <c r="R36" s="10">
-        <f t="shared" si="121"/>
+        <f t="shared" si="127"/>
         <v>0.43594816839553041</v>
       </c>
       <c r="S36" s="10">
-        <f t="shared" ref="S36" si="122">S20/O20-1</f>
+        <f t="shared" ref="S36" si="128">S20/O20-1</f>
         <v>0.43823888034777081</v>
       </c>
       <c r="T36" s="10">
-        <f t="shared" ref="T36" si="123">T20/P20-1</f>
+        <f t="shared" ref="T36" si="129">T20/P20-1</f>
         <v>0.27181932697498645</v>
       </c>
       <c r="U36" s="10">
-        <f t="shared" ref="U36" si="124">U20/Q20-1</f>
+        <f t="shared" ref="U36" si="130">U20/Q20-1</f>
         <v>0.15255083467679031</v>
       </c>
       <c r="V36" s="10">
-        <f t="shared" ref="V36" si="125">V20/R20-1</f>
+        <f t="shared" ref="V36" si="131">V20/R20-1</f>
         <v>9.4436701047349692E-2</v>
       </c>
       <c r="W36" s="10">
@@ -6784,7 +7126,7 @@
         <v>7.3038574245747334E-2</v>
       </c>
       <c r="X36" s="10">
-        <f t="shared" ref="X36:AE36" si="126">X20/T20-1</f>
+        <f t="shared" ref="X36:AE36" si="132">X20/T20-1</f>
         <v>7.2108241952600016E-2</v>
       </c>
       <c r="Y36" s="10">
@@ -6792,7 +7134,7 @@
         <v>0.14699671515720314</v>
       </c>
       <c r="Z36" s="10">
-        <f t="shared" si="126"/>
+        <f t="shared" si="132"/>
         <v>8.5814921549791867E-2</v>
       </c>
       <c r="AA36" s="10">
@@ -6800,19 +7142,19 @@
         <v>9.3727456975026602E-2</v>
       </c>
       <c r="AB36" s="10">
-        <f t="shared" si="126"/>
+        <f t="shared" si="132"/>
         <v>0.10845967302901816</v>
       </c>
       <c r="AC36" s="10">
-        <f t="shared" si="126"/>
+        <f t="shared" si="132"/>
         <v>0.125742519728405</v>
       </c>
       <c r="AD36" s="10">
-        <f t="shared" si="126"/>
+        <f t="shared" si="132"/>
         <v>0.13911825420230017</v>
       </c>
       <c r="AE36" s="10">
-        <f t="shared" si="126"/>
+        <f t="shared" si="132"/>
         <v>0.12527677884388888</v>
       </c>
       <c r="AF36" s="10">
@@ -6820,123 +7162,135 @@
         <v>0.10116607011303502</v>
       </c>
       <c r="AG36" s="10">
-        <f t="shared" ref="AG36:AL36" si="127">AG20/AC20-1</f>
+        <f t="shared" ref="AG36:AL36" si="133">AG20/AC20-1</f>
         <v>0.11038348371225104</v>
       </c>
       <c r="AH36" s="10">
-        <f t="shared" si="127"/>
+        <f t="shared" si="133"/>
         <v>0.10491230341078239</v>
       </c>
       <c r="AI36" s="10">
-        <f t="shared" si="127"/>
+        <f t="shared" si="133"/>
         <v>8.6202926461660834E-2</v>
       </c>
       <c r="AJ36" s="10">
-        <f t="shared" si="127"/>
+        <f t="shared" si="133"/>
         <v>0.13329008366108486</v>
       </c>
       <c r="AK36" s="10">
-        <f t="shared" si="127"/>
-        <v>0.10000000000000009</v>
+        <f t="shared" si="133"/>
+        <v>0.13401562214795093</v>
       </c>
       <c r="AL36" s="10">
-        <f t="shared" si="127"/>
-        <v>0.10000000000000009</v>
-      </c>
-      <c r="AM36" s="10"/>
-      <c r="AN36" s="10"/>
-      <c r="AO36" s="10"/>
-      <c r="AP36" s="10"/>
+        <f t="shared" si="133"/>
+        <v>0.13628908579705201</v>
+      </c>
+      <c r="AM36" s="10">
+        <f t="shared" ref="AM36" si="134">AM20/AI20-1</f>
+        <v>0.16607244952366274</v>
+      </c>
+      <c r="AN36" s="10">
+        <f>AN20/AJ20-1</f>
+        <v>0.19620517346245125</v>
+      </c>
+      <c r="AO36" s="10">
+        <f t="shared" ref="AO36" si="135">AO20/AK20-1</f>
+        <v>0.12999999999999989</v>
+      </c>
+      <c r="AP36" s="10">
+        <f t="shared" ref="AP36" si="136">AP20/AL20-1</f>
+        <v>0.12999999999999989</v>
+      </c>
       <c r="AU36" s="15">
-        <f t="shared" ref="AU36:AV36" si="128">AU20/AT20-1</f>
+        <f t="shared" ref="AU36:AV36" si="137">AU20/AT20-1</f>
         <v>3.1263372285789677</v>
       </c>
       <c r="AV36" s="15">
-        <f t="shared" si="128"/>
+        <f t="shared" si="137"/>
         <v>1.6890585567192891</v>
       </c>
       <c r="AW36" s="15">
-        <f t="shared" ref="AW36" si="129">AW20/AV20-1</f>
+        <f t="shared" ref="AW36" si="138">AW20/AV20-1</f>
         <v>0.68430132470321792</v>
       </c>
       <c r="AX36" s="15">
-        <f t="shared" ref="AX36" si="130">AX20/AW20-1</f>
+        <f t="shared" ref="AX36" si="139">AX20/AW20-1</f>
         <v>0.1305040617556299</v>
       </c>
       <c r="AY36" s="15">
-        <f t="shared" ref="AY36" si="131">AY20/AX20-1</f>
+        <f t="shared" ref="AY36" si="140">AY20/AX20-1</f>
         <v>0.25957418461821291</v>
       </c>
       <c r="AZ36" s="15">
-        <f t="shared" ref="AZ36" si="132">AZ20/AY20-1</f>
+        <f t="shared" ref="AZ36" si="141">AZ20/AY20-1</f>
         <v>0.3383637567455966</v>
       </c>
       <c r="BA36" s="15">
-        <f t="shared" ref="BA36" si="133">BA20/AZ20-1</f>
+        <f t="shared" ref="BA36" si="142">BA20/AZ20-1</f>
         <v>0.31485481977597884</v>
       </c>
       <c r="BB36" s="15">
-        <f t="shared" ref="BB36" si="134">BB20/BA20-1</f>
+        <f t="shared" ref="BB36" si="143">BB20/BA20-1</f>
         <v>0.22670134373645423</v>
       </c>
       <c r="BC36" s="15">
-        <f t="shared" ref="BC36" si="135">BC20/BB20-1</f>
+        <f t="shared" ref="BC36" si="144">BC20/BB20-1</f>
         <v>0.26160188457008249</v>
       </c>
       <c r="BD36" s="15">
-        <f t="shared" ref="BD36" si="136">BD20/BC20-1</f>
+        <f t="shared" ref="BD36" si="145">BD20/BC20-1</f>
         <v>0.38502474092054895</v>
       </c>
       <c r="BE36" s="15">
-        <f t="shared" ref="BE36" si="137">BE20/BD20-1</f>
+        <f t="shared" ref="BE36" si="146">BE20/BD20-1</f>
         <v>0.29194472531176263</v>
       </c>
       <c r="BF36" s="15">
-        <f t="shared" ref="BF36" si="138">BF20/BE20-1</f>
+        <f t="shared" ref="BF36" si="147">BF20/BE20-1</f>
         <v>0.27877491391004905</v>
       </c>
       <c r="BG36" s="15">
-        <f t="shared" ref="BG36" si="139">BG20/BF20-1</f>
+        <f t="shared" ref="BG36" si="148">BG20/BF20-1</f>
         <v>0.39556897466236896</v>
       </c>
       <c r="BH36" s="15">
-        <f t="shared" ref="BH36" si="140">BH20/BG20-1</f>
+        <f t="shared" ref="BH36" si="149">BH20/BG20-1</f>
         <v>0.40559583674424049</v>
       </c>
       <c r="BI36" s="15">
-        <f t="shared" ref="BI36" si="141">BI20/BH20-1</f>
+        <f t="shared" ref="BI36" si="150">BI20/BH20-1</f>
         <v>0.27073236682821311</v>
       </c>
       <c r="BJ36" s="15">
-        <f t="shared" ref="BJ36:BN36" si="142">BJ20/BI20-1</f>
+        <f t="shared" ref="BJ36:BN36" si="151">BJ20/BI20-1</f>
         <v>0.21866662301736706</v>
       </c>
       <c r="BK36" s="15">
-        <f t="shared" si="142"/>
+        <f t="shared" si="151"/>
         <v>0.1952398861011122</v>
       </c>
       <c r="BL36" s="15">
-        <f t="shared" si="142"/>
+        <f t="shared" si="151"/>
         <v>0.20247673843664304</v>
       </c>
       <c r="BM36" s="15">
-        <f t="shared" si="142"/>
+        <f t="shared" si="151"/>
         <v>0.27083528026465808</v>
       </c>
       <c r="BN36" s="15">
-        <f t="shared" si="142"/>
+        <f t="shared" si="151"/>
         <v>0.30796326119408479</v>
       </c>
       <c r="BO36" s="15">
-        <f t="shared" ref="BO36" si="143">BO20/BN20-1</f>
+        <f t="shared" ref="BO36" si="152">BO20/BN20-1</f>
         <v>0.3093396152159491</v>
       </c>
       <c r="BP36" s="15">
-        <f t="shared" ref="BP36" si="144">BP20/BO20-1</f>
+        <f t="shared" ref="BP36" si="153">BP20/BO20-1</f>
         <v>0.20454125820676983</v>
       </c>
       <c r="BQ36" s="15">
-        <f t="shared" ref="BQ36" si="145">BQ20/BP20-1</f>
+        <f t="shared" ref="BQ36" si="154">BQ20/BP20-1</f>
         <v>0.37623430604373276</v>
       </c>
       <c r="BR36" s="15">
@@ -6944,7 +7298,7 @@
         <v>0.21695366571345676</v>
       </c>
       <c r="BS36" s="15">
-        <f t="shared" ref="BS36:CA36" si="146">BS20/BR20-1</f>
+        <f t="shared" ref="BS36:CA36" si="155">BS20/BR20-1</f>
         <v>9.399517263985091E-2</v>
       </c>
       <c r="BT36" s="15">
@@ -6952,32 +7306,32 @@
         <v>0.1182957412988368</v>
       </c>
       <c r="BU36" s="15">
-        <f t="shared" si="146"/>
+        <f t="shared" si="155"/>
         <v>0.1099089224666614</v>
       </c>
       <c r="BV36" s="15">
-        <f t="shared" si="146"/>
-        <v>7.2097658313465374E-2</v>
+        <f t="shared" si="155"/>
+        <v>8.263626659393486E-2</v>
       </c>
       <c r="BW36" s="15">
-        <f t="shared" si="146"/>
-        <v>8.4845322644705679E-2</v>
+        <f t="shared" si="155"/>
+        <v>8.5966262404214566E-2</v>
       </c>
       <c r="BX36" s="15">
-        <f t="shared" si="146"/>
-        <v>8.7798486748400739E-2</v>
+        <f t="shared" si="155"/>
+        <v>8.9005367380824874E-2</v>
       </c>
       <c r="BY36" s="15">
-        <f t="shared" si="146"/>
-        <v>7.1766336710576972E-2</v>
+        <f t="shared" si="155"/>
+        <v>7.2693615863370198E-2</v>
       </c>
       <c r="BZ36" s="15">
-        <f t="shared" si="146"/>
-        <v>6.167758603707818E-2</v>
+        <f t="shared" si="155"/>
+        <v>6.216454440342245E-2</v>
       </c>
       <c r="CA36" s="15">
-        <f t="shared" si="146"/>
-        <v>6.2099101280581381E-2</v>
+        <f t="shared" si="155"/>
+        <v>6.2597858697383435E-2</v>
       </c>
     </row>
     <row r="37" spans="2:82" s="11" customFormat="1" ht="13" x14ac:dyDescent="0.3">
@@ -7084,103 +7438,109 @@
       <c r="M38" s="8"/>
       <c r="N38" s="8"/>
       <c r="O38" s="8">
-        <f t="shared" ref="O38:R39" si="147">+O18/K18-1</f>
+        <f t="shared" ref="O38:R39" si="156">+O18/K18-1</f>
         <v>0.22045911968030807</v>
       </c>
       <c r="P38" s="8">
-        <f t="shared" si="147"/>
+        <f t="shared" si="156"/>
         <v>0.40127175368139234</v>
       </c>
       <c r="Q38" s="8">
-        <f t="shared" si="147"/>
+        <f t="shared" si="156"/>
         <v>0.32844988168957356</v>
       </c>
       <c r="R38" s="8">
-        <f t="shared" si="147"/>
+        <f t="shared" si="156"/>
         <v>0.40588025800324479</v>
       </c>
       <c r="S38" s="8">
-        <f t="shared" ref="S38:W38" si="148">+S18/O18-1</f>
+        <f t="shared" ref="S38:W38" si="157">+S18/O18-1</f>
         <v>0.37403503740350375</v>
       </c>
       <c r="T38" s="8">
-        <f t="shared" si="148"/>
+        <f t="shared" si="157"/>
         <v>0.15444630204601539</v>
       </c>
       <c r="U38" s="8">
-        <f t="shared" si="148"/>
+        <f t="shared" si="157"/>
         <v>3.9830219426232549E-2</v>
       </c>
       <c r="V38" s="8">
-        <f t="shared" si="148"/>
+        <f t="shared" si="157"/>
         <v>5.0664264805224679E-3</v>
       </c>
       <c r="W38" s="8">
-        <f t="shared" si="148"/>
+        <f t="shared" si="157"/>
         <v>-1.8020211859247515E-2</v>
       </c>
       <c r="X38" s="8">
-        <f t="shared" ref="X38:AF38" si="149">+X18/T18-1</f>
+        <f t="shared" ref="X38:AF38" si="158">+X18/T18-1</f>
         <v>-2.4636231984001111E-2</v>
       </c>
       <c r="Y38" s="8">
-        <f t="shared" si="149"/>
+        <f t="shared" si="158"/>
         <v>8.1347036956046281E-2</v>
       </c>
       <c r="Z38" s="8">
-        <f t="shared" si="149"/>
+        <f t="shared" si="158"/>
         <v>-1.2392181023860194E-2</v>
       </c>
       <c r="AA38" s="8">
-        <f t="shared" si="149"/>
+        <f t="shared" si="158"/>
         <v>9.317155256398868E-3</v>
       </c>
       <c r="AB38" s="8">
-        <f t="shared" si="149"/>
+        <f t="shared" si="158"/>
         <v>4.342907644719407E-2</v>
       </c>
       <c r="AC38" s="8">
-        <f t="shared" si="149"/>
+        <f t="shared" si="158"/>
         <v>6.4560161779575242E-2</v>
       </c>
       <c r="AD38" s="8">
-        <f t="shared" si="149"/>
+        <f t="shared" si="158"/>
         <v>8.7507620762501626E-2</v>
       </c>
       <c r="AE38" s="8">
-        <f t="shared" si="149"/>
+        <f t="shared" si="158"/>
         <v>6.9040557378775347E-2</v>
       </c>
       <c r="AF38" s="8">
-        <f t="shared" si="149"/>
+        <f t="shared" si="158"/>
         <v>4.2976690608483636E-2</v>
       </c>
       <c r="AG38" s="8">
-        <f t="shared" ref="AG38:AL38" si="150">+AG18/AC18-1</f>
+        <f t="shared" ref="AG38:AL38" si="159">+AG18/AC18-1</f>
         <v>7.0127115290243847E-2</v>
       </c>
       <c r="AH38" s="8">
-        <f t="shared" si="150"/>
+        <f t="shared" si="159"/>
         <v>7.200500632309037E-2</v>
       </c>
       <c r="AI38" s="8">
-        <f t="shared" si="150"/>
+        <f t="shared" si="159"/>
         <v>5.0151850939834208E-2</v>
       </c>
       <c r="AJ38" s="8">
-        <f t="shared" si="150"/>
+        <f t="shared" si="159"/>
         <v>0.10844743296139292</v>
       </c>
       <c r="AK38" s="8">
-        <f t="shared" si="150"/>
-        <v>-1</v>
+        <f t="shared" si="159"/>
+        <v>9.5516338515702515E-2</v>
       </c>
       <c r="AL38" s="8">
-        <f t="shared" si="150"/>
-        <v>-1</v>
-      </c>
-      <c r="AM38" s="8"/>
-      <c r="AN38" s="8"/>
+        <f t="shared" si="159"/>
+        <v>9.4447011894048138E-2</v>
+      </c>
+      <c r="AM38" s="8">
+        <f t="shared" ref="AM38:AM39" si="160">+AM18/AI18-1</f>
+        <v>0.1146474910114117</v>
+      </c>
+      <c r="AN38" s="8">
+        <f t="shared" ref="AN38:AN39" si="161">+AN18/AJ18-1</f>
+        <v>0.13709228379685245</v>
+      </c>
       <c r="AO38" s="8"/>
       <c r="AP38" s="8"/>
       <c r="BJ38" s="13"/>
@@ -7212,55 +7572,55 @@
       <c r="M39" s="8"/>
       <c r="N39" s="8"/>
       <c r="O39" s="8">
-        <f t="shared" si="147"/>
+        <f t="shared" si="156"/>
         <v>0.32238265727662596</v>
       </c>
       <c r="P39" s="8">
-        <f t="shared" si="147"/>
+        <f t="shared" si="156"/>
         <v>0.40365906780891536</v>
       </c>
       <c r="Q39" s="8">
-        <f t="shared" si="147"/>
+        <f t="shared" si="156"/>
         <v>0.43351512146752613</v>
       </c>
       <c r="R39" s="8">
-        <f t="shared" si="147"/>
+        <f t="shared" si="156"/>
         <v>0.47713782355332701</v>
       </c>
       <c r="S39" s="8">
-        <f t="shared" ref="S39" si="151">+S19/O19-1</f>
+        <f t="shared" ref="S39" si="162">+S19/O19-1</f>
         <v>0.5181636964089138</v>
       </c>
       <c r="T39" s="8">
-        <f t="shared" ref="T39" si="152">+T19/P19-1</f>
+        <f t="shared" ref="T39" si="163">+T19/P19-1</f>
         <v>0.42433019551049966</v>
       </c>
       <c r="U39" s="8">
-        <f t="shared" ref="U39" si="153">+U19/Q19-1</f>
+        <f t="shared" ref="U39" si="164">+U19/Q19-1</f>
         <v>0.28970971386410271</v>
       </c>
       <c r="V39" s="8">
-        <f t="shared" ref="V39" si="154">+V19/R19-1</f>
+        <f t="shared" ref="V39" si="165">+V19/R19-1</f>
         <v>0.21095799922934355</v>
       </c>
       <c r="W39" s="8">
-        <f t="shared" ref="W39:AA39" si="155">+W19/S19-1</f>
+        <f t="shared" ref="W39:AA39" si="166">+W19/S19-1</f>
         <v>0.17563250827993016</v>
       </c>
       <c r="X39" s="8">
-        <f t="shared" si="155"/>
+        <f t="shared" si="166"/>
         <v>0.17399593289273008</v>
       </c>
       <c r="Y39" s="8">
-        <f t="shared" si="155"/>
+        <f t="shared" si="166"/>
         <v>0.21140231693363853</v>
       </c>
       <c r="Z39" s="8">
-        <f t="shared" si="155"/>
+        <f t="shared" si="166"/>
         <v>0.19208739923631746</v>
       </c>
       <c r="AA39" s="8">
-        <f t="shared" si="155"/>
+        <f t="shared" si="166"/>
         <v>0.17316508026471511</v>
       </c>
       <c r="AB39" s="8">
@@ -7284,31 +7644,37 @@
         <v>0.14675319504717921</v>
       </c>
       <c r="AG39" s="8">
-        <f t="shared" ref="AG39:AL39" si="156">+AG19/AC19-1</f>
+        <f t="shared" ref="AG39:AL39" si="167">+AG19/AC19-1</f>
         <v>0.14220642706977671</v>
       </c>
       <c r="AH39" s="8">
-        <f t="shared" si="156"/>
+        <f t="shared" si="167"/>
         <v>0.13197795363400466</v>
       </c>
       <c r="AI39" s="8">
-        <f t="shared" si="156"/>
+        <f t="shared" si="167"/>
         <v>0.11285468093885775</v>
       </c>
       <c r="AJ39" s="8">
-        <f t="shared" si="156"/>
+        <f t="shared" si="167"/>
         <v>0.15099121619275779</v>
       </c>
       <c r="AK39" s="8">
-        <f t="shared" si="156"/>
-        <v>-1</v>
+        <f t="shared" si="167"/>
+        <v>0.16252903282352427</v>
       </c>
       <c r="AL39" s="8">
-        <f t="shared" si="156"/>
-        <v>-1</v>
-      </c>
-      <c r="AM39" s="8"/>
-      <c r="AN39" s="8"/>
+        <f t="shared" si="167"/>
+        <v>0.168880131860637</v>
+      </c>
+      <c r="AM39" s="8">
+        <f t="shared" si="160"/>
+        <v>0.20194771911840093</v>
+      </c>
+      <c r="AN39" s="8">
+        <f t="shared" si="161"/>
+        <v>0.23676801801801806</v>
+      </c>
       <c r="AO39" s="8"/>
       <c r="AP39" s="8"/>
       <c r="BJ39" s="13"/>
@@ -7335,39 +7701,39 @@
         <v>56</v>
       </c>
       <c r="N40" s="8">
-        <f t="shared" ref="N40" si="157">+N11/J11-1</f>
+        <f t="shared" ref="N40" si="168">+N11/J11-1</f>
         <v>0.14652704535181549</v>
       </c>
       <c r="O40" s="8">
-        <f t="shared" ref="O40" si="158">+O11/K11-1</f>
+        <f t="shared" ref="O40" si="169">+O11/K11-1</f>
         <v>0.24252491694352152</v>
       </c>
       <c r="P40" s="8">
-        <f t="shared" ref="P40" si="159">+P11/L11-1</f>
+        <f t="shared" ref="P40" si="170">+P11/L11-1</f>
         <v>0.47798924419540789</v>
       </c>
       <c r="Q40" s="8">
-        <f t="shared" ref="Q40" si="160">+Q11/M11-1</f>
+        <f t="shared" ref="Q40" si="171">+Q11/M11-1</f>
         <v>0.37989097862381915</v>
       </c>
       <c r="R40" s="8">
-        <f t="shared" ref="R40:V40" si="161">+R11/N11-1</f>
+        <f t="shared" ref="R40:V40" si="172">+R11/N11-1</f>
         <v>0.45543947258908823</v>
       </c>
       <c r="S40" s="8">
-        <f t="shared" si="161"/>
+        <f t="shared" si="172"/>
         <v>0.44333187820582776</v>
       </c>
       <c r="T40" s="8">
-        <f t="shared" si="161"/>
+        <f t="shared" si="172"/>
         <v>0.15820550810528156</v>
       </c>
       <c r="U40" s="8">
-        <f t="shared" si="161"/>
+        <f t="shared" si="172"/>
         <v>3.2926577042399208E-2</v>
       </c>
       <c r="V40" s="8">
-        <f t="shared" si="161"/>
+        <f t="shared" si="172"/>
         <v>-5.6583046154309313E-3</v>
       </c>
       <c r="W40" s="8">
@@ -7375,31 +7741,31 @@
         <v>-3.3496531256497986E-2</v>
       </c>
       <c r="X40" s="8">
-        <f t="shared" ref="X40:AD40" si="162">+X11/T11-1</f>
+        <f t="shared" ref="X40:AD40" si="173">+X11/T11-1</f>
         <v>-4.3305679402524611E-2</v>
       </c>
       <c r="Y40" s="8">
-        <f t="shared" si="162"/>
+        <f t="shared" si="173"/>
         <v>7.102238596772259E-2</v>
       </c>
       <c r="Z40" s="8">
-        <f t="shared" si="162"/>
+        <f t="shared" si="173"/>
         <v>-2.3367385546727237E-2</v>
       </c>
       <c r="AA40" s="8">
-        <f t="shared" si="162"/>
+        <f t="shared" si="173"/>
         <v>-6.4542627471686487E-4</v>
       </c>
       <c r="AB40" s="8">
-        <f t="shared" si="162"/>
+        <f t="shared" si="173"/>
         <v>4.1510175990561393E-2</v>
       </c>
       <c r="AC40" s="8">
-        <f t="shared" si="162"/>
+        <f t="shared" si="173"/>
         <v>7.0631344762474457E-2</v>
       </c>
       <c r="AD40" s="8">
-        <f t="shared" si="162"/>
+        <f t="shared" si="173"/>
         <v>9.3164525576854507E-2</v>
       </c>
       <c r="AE40" s="8">
@@ -7411,40 +7777,46 @@
         <v>4.5802967941698469E-2</v>
       </c>
       <c r="AG40" s="8">
-        <f t="shared" ref="AG40:AL40" si="163">+AG11/AC11-1</f>
+        <f t="shared" ref="AG40:AL40" si="174">+AG11/AC11-1</f>
         <v>7.2362791834738927E-2</v>
       </c>
       <c r="AH40" s="8">
-        <f t="shared" si="163"/>
+        <f t="shared" si="174"/>
         <v>7.1063039564520869E-2</v>
       </c>
       <c r="AI40" s="8">
-        <f t="shared" si="163"/>
+        <f t="shared" si="174"/>
         <v>5.0064020486555671E-2</v>
       </c>
       <c r="AJ40" s="8">
-        <f t="shared" si="163"/>
+        <f t="shared" si="174"/>
         <v>0.10999783362218363</v>
       </c>
       <c r="AK40" s="8">
-        <f t="shared" si="163"/>
-        <v>-1</v>
+        <f t="shared" si="174"/>
+        <v>9.7637231114946932E-2</v>
       </c>
       <c r="AL40" s="8">
-        <f t="shared" si="163"/>
-        <v>-1</v>
-      </c>
-      <c r="AM40" s="8"/>
-      <c r="AN40" s="8"/>
+        <f t="shared" si="174"/>
+        <v>9.8364127269839674E-2</v>
+      </c>
+      <c r="AM40" s="8">
+        <f t="shared" ref="AM40" si="175">+AM11/AI11-1</f>
+        <v>0.11927116902119961</v>
+      </c>
+      <c r="AN40" s="8">
+        <f t="shared" ref="AN40" si="176">+AN11/AJ11-1</f>
+        <v>0.1455151663007237</v>
+      </c>
       <c r="AO40" s="8"/>
       <c r="AP40" s="8"/>
       <c r="BO40" s="13"/>
       <c r="BP40" s="13">
-        <f t="shared" ref="BP40" si="164">BP11/BO11-1</f>
+        <f t="shared" ref="BP40" si="177">BP11/BO11-1</f>
         <v>0.14847097660728359</v>
       </c>
       <c r="BQ40" s="13">
-        <f t="shared" ref="BQ40" si="165">BQ11/BP11-1</f>
+        <f t="shared" ref="BQ40" si="178">BQ11/BP11-1</f>
         <v>0.39719073679440986</v>
       </c>
       <c r="BR40" s="13">
@@ -7452,39 +7824,39 @@
         <v>0.12529072860769497</v>
       </c>
       <c r="BS40" s="13">
-        <f t="shared" ref="BS40:CA40" si="166">BS11/BR11-1</f>
+        <f t="shared" ref="BS40:CA40" si="179">BS11/BR11-1</f>
         <v>-9.3256782618484912E-3</v>
       </c>
       <c r="BT40" s="13">
-        <f t="shared" si="166"/>
+        <f t="shared" si="179"/>
         <v>5.3944473736841081E-2</v>
       </c>
       <c r="BU40" s="13">
-        <f t="shared" si="166"/>
+        <f t="shared" si="179"/>
         <v>6.5367961634005045E-2</v>
       </c>
       <c r="BV40" s="13">
-        <f t="shared" si="166"/>
+        <f t="shared" si="179"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="BW40" s="13">
-        <f t="shared" si="166"/>
+        <f t="shared" si="179"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="BX40" s="13">
-        <f t="shared" si="166"/>
+        <f t="shared" si="179"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="BY40" s="13">
-        <f t="shared" si="166"/>
+        <f t="shared" si="179"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="BZ40" s="13">
-        <f t="shared" si="166"/>
+        <f t="shared" si="179"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="CA40" s="13">
-        <f t="shared" si="166"/>
+        <f t="shared" si="179"/>
         <v>5.0000000000000044E-2</v>
       </c>
     </row>
@@ -7493,39 +7865,39 @@
         <v>57</v>
       </c>
       <c r="N41" s="8">
-        <f t="shared" ref="N41:V41" si="167">+N13/J13-1</f>
+        <f t="shared" ref="N41:V41" si="180">+N13/J13-1</f>
         <v>0.30359411193304942</v>
       </c>
       <c r="O41" s="8">
-        <f t="shared" si="167"/>
+        <f t="shared" si="180"/>
         <v>0.29961403823714217</v>
       </c>
       <c r="P41" s="8">
-        <f t="shared" si="167"/>
+        <f t="shared" si="180"/>
         <v>0.52106671125229886</v>
       </c>
       <c r="Q41" s="8">
-        <f t="shared" si="167"/>
+        <f t="shared" si="180"/>
         <v>0.54677565849227983</v>
       </c>
       <c r="R41" s="8">
-        <f t="shared" si="167"/>
+        <f t="shared" si="180"/>
         <v>0.56637624670411557</v>
       </c>
       <c r="S41" s="8">
-        <f t="shared" si="167"/>
+        <f t="shared" si="180"/>
         <v>0.63747496374058987</v>
       </c>
       <c r="T41" s="8">
-        <f t="shared" si="167"/>
+        <f t="shared" si="180"/>
         <v>0.37867546029128873</v>
       </c>
       <c r="U41" s="8">
-        <f t="shared" si="167"/>
+        <f t="shared" si="180"/>
         <v>0.18672930123311793</v>
       </c>
       <c r="V41" s="8">
-        <f t="shared" si="167"/>
+        <f t="shared" si="180"/>
         <v>0.10952537783144867</v>
       </c>
       <c r="W41" s="8">
@@ -7533,76 +7905,82 @@
         <v>6.8581551309629285E-2</v>
       </c>
       <c r="X41" s="8">
-        <f t="shared" ref="X41:AD41" si="168">+X13/T13-1</f>
+        <f t="shared" ref="X41:AD41" si="181">+X13/T13-1</f>
         <v>9.1329479768786026E-2</v>
       </c>
       <c r="Y41" s="8">
-        <f t="shared" si="168"/>
+        <f t="shared" si="181"/>
         <v>0.18200560778492503</v>
       </c>
       <c r="Z41" s="8">
-        <f t="shared" si="168"/>
+        <f t="shared" si="181"/>
         <v>0.19851583113456472</v>
       </c>
       <c r="AA41" s="8">
-        <f t="shared" si="168"/>
+        <f t="shared" si="181"/>
         <v>0.177027827116637</v>
       </c>
       <c r="AB41" s="8">
-        <f t="shared" si="168"/>
+        <f t="shared" si="181"/>
         <v>0.18103448275862077</v>
       </c>
       <c r="AC41" s="8">
-        <f t="shared" si="168"/>
+        <f t="shared" si="181"/>
         <v>0.19800460475825021</v>
       </c>
       <c r="AD41" s="8">
-        <f t="shared" si="168"/>
+        <f t="shared" si="181"/>
         <v>0.19868460882247718</v>
       </c>
       <c r="AE41" s="8">
-        <f t="shared" ref="AE41:AL43" si="169">+AE13/AA13-1</f>
+        <f t="shared" ref="AE41:AL43" si="182">+AE13/AA13-1</f>
         <v>0.16016096579476868</v>
       </c>
       <c r="AF41" s="8">
-        <f t="shared" si="169"/>
+        <f t="shared" si="182"/>
         <v>0.11966472844240994</v>
       </c>
       <c r="AG41" s="8">
-        <f t="shared" si="169"/>
+        <f t="shared" si="182"/>
         <v>0.10255663618892319</v>
       </c>
       <c r="AH41" s="8">
-        <f t="shared" si="169"/>
+        <f t="shared" si="182"/>
         <v>9.0130627424872101E-2</v>
       </c>
       <c r="AI41" s="8">
-        <f t="shared" si="169"/>
+        <f t="shared" si="182"/>
         <v>5.538212510116769E-2</v>
       </c>
       <c r="AJ41" s="8">
-        <f t="shared" si="169"/>
+        <f t="shared" si="182"/>
         <v>0.1145548465512003</v>
       </c>
       <c r="AK41" s="8">
-        <f t="shared" si="169"/>
-        <v>-1</v>
+        <f t="shared" si="182"/>
+        <v>0.12206845552503687</v>
       </c>
       <c r="AL41" s="8">
-        <f t="shared" si="169"/>
-        <v>-1</v>
-      </c>
-      <c r="AM41" s="8"/>
-      <c r="AN41" s="8"/>
+        <f t="shared" si="182"/>
+        <v>0.11226703169421914</v>
+      </c>
+      <c r="AM41" s="8">
+        <f t="shared" ref="AM41:AM43" si="183">+AM13/AI13-1</f>
+        <v>0.1387489044697634</v>
+      </c>
+      <c r="AN41" s="8">
+        <f t="shared" ref="AN41:AN43" si="184">+AN13/AJ13-1</f>
+        <v>0.15941310597799152</v>
+      </c>
       <c r="AO41" s="8"/>
       <c r="AP41" s="8"/>
       <c r="BO41" s="13"/>
       <c r="BP41" s="13">
-        <f t="shared" ref="BP41" si="170">BP13/BO13-1</f>
+        <f t="shared" ref="BP41" si="185">BP13/BO13-1</f>
         <v>0.25771435255585451</v>
       </c>
       <c r="BQ41" s="13">
-        <f t="shared" ref="BQ41" si="171">BQ13/BP13-1</f>
+        <f t="shared" ref="BQ41" si="186">BQ13/BP13-1</f>
         <v>0.4961961273041795</v>
       </c>
       <c r="BR41" s="13">
@@ -7610,39 +7988,39 @@
         <v>0.28505538495965776</v>
       </c>
       <c r="BS41" s="13">
-        <f t="shared" ref="BS41:CA41" si="172">BS13/BR13-1</f>
+        <f t="shared" ref="BS41:CA41" si="187">BS13/BR13-1</f>
         <v>0.13882708047133496</v>
       </c>
       <c r="BT41" s="13">
-        <f t="shared" si="172"/>
+        <f t="shared" si="187"/>
         <v>0.18975330456352579</v>
       </c>
       <c r="BU41" s="13">
-        <f t="shared" si="172"/>
+        <f t="shared" si="187"/>
         <v>0.11490649968226307</v>
       </c>
       <c r="BV41" s="13">
-        <f t="shared" si="172"/>
+        <f t="shared" si="187"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="BW41" s="13">
-        <f t="shared" si="172"/>
+        <f t="shared" si="187"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="BX41" s="13">
-        <f t="shared" si="172"/>
+        <f t="shared" si="187"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="BY41" s="13">
-        <f t="shared" si="172"/>
+        <f t="shared" si="187"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="BZ41" s="13">
-        <f t="shared" si="172"/>
+        <f t="shared" si="187"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="CA41" s="13">
-        <f t="shared" si="172"/>
+        <f t="shared" si="187"/>
         <v>5.0000000000000044E-2</v>
       </c>
     </row>
@@ -7651,39 +8029,39 @@
         <v>58</v>
       </c>
       <c r="N42" s="8">
-        <f t="shared" ref="N42:V43" si="173">+N14/J14-1</f>
+        <f t="shared" ref="N42:V43" si="188">+N14/J14-1</f>
         <v>0.3223036120232381</v>
       </c>
       <c r="O42" s="8">
-        <f t="shared" si="173"/>
+        <f t="shared" si="188"/>
         <v>0.27959465684016571</v>
       </c>
       <c r="P42" s="8">
-        <f t="shared" si="173"/>
+        <f t="shared" si="188"/>
         <v>0.28699743370402042</v>
       </c>
       <c r="Q42" s="8">
-        <f t="shared" si="173"/>
+        <f t="shared" si="188"/>
         <v>0.32580189630825096</v>
       </c>
       <c r="R42" s="8">
-        <f t="shared" si="173"/>
+        <f t="shared" si="188"/>
         <v>0.34880611270296091</v>
       </c>
       <c r="S42" s="8">
-        <f t="shared" si="173"/>
+        <f t="shared" si="188"/>
         <v>0.36429085673146155</v>
       </c>
       <c r="T42" s="8">
-        <f t="shared" si="173"/>
+        <f t="shared" si="188"/>
         <v>0.31555333998005985</v>
       </c>
       <c r="U42" s="8">
-        <f t="shared" si="173"/>
+        <f t="shared" si="188"/>
         <v>0.23980523432744971</v>
       </c>
       <c r="V42" s="8">
-        <f t="shared" si="173"/>
+        <f t="shared" si="188"/>
         <v>0.15040362554878905</v>
       </c>
       <c r="W42" s="8">
@@ -7691,76 +8069,82 @@
         <v>0.10949868073878632</v>
       </c>
       <c r="X42" s="8">
-        <f t="shared" ref="X42:AD43" si="174">+X14/T14-1</f>
+        <f t="shared" ref="X42:AD43" si="189">+X14/T14-1</f>
         <v>0.10092206643930779</v>
       </c>
       <c r="Y42" s="8">
-        <f t="shared" si="174"/>
+        <f t="shared" si="189"/>
         <v>9.2660775650466265E-2</v>
       </c>
       <c r="Z42" s="8">
-        <f t="shared" si="174"/>
+        <f t="shared" si="189"/>
         <v>0.13123230333620572</v>
       </c>
       <c r="AA42" s="8">
-        <f t="shared" si="174"/>
+        <f t="shared" si="189"/>
         <v>0.14827586206896548</v>
       </c>
       <c r="AB42" s="8">
-        <f t="shared" si="174"/>
+        <f t="shared" si="189"/>
         <v>0.13515374024782001</v>
       </c>
       <c r="AC42" s="8">
-        <f t="shared" si="174"/>
+        <f t="shared" si="189"/>
         <v>0.14231158036616876</v>
       </c>
       <c r="AD42" s="8">
-        <f t="shared" si="174"/>
+        <f t="shared" si="189"/>
         <v>0.14136467515507678</v>
       </c>
       <c r="AE42" s="8">
-        <f t="shared" si="169"/>
-        <v>0.22439681060370709</v>
+        <f t="shared" si="182"/>
+        <v>0.1102826964895931</v>
       </c>
       <c r="AF42" s="8">
-        <f t="shared" si="169"/>
-        <v>0.29078229229836272</v>
+        <f t="shared" si="182"/>
+        <v>9.824135839902981E-2</v>
       </c>
       <c r="AG42" s="8">
-        <f t="shared" si="169"/>
-        <v>0.40914454277286127</v>
+        <f t="shared" si="182"/>
+        <v>0.10894788593903648</v>
       </c>
       <c r="AH42" s="8">
-        <f t="shared" si="169"/>
-        <v>0.64836003051106017</v>
+        <f t="shared" si="182"/>
+        <v>9.7254004576659003E-2</v>
       </c>
       <c r="AI42" s="8">
-        <f t="shared" si="169"/>
-        <v>0.17735115020297698</v>
+        <f t="shared" si="182"/>
+        <v>9.2613318410744272E-2</v>
       </c>
       <c r="AJ42" s="8">
-        <f t="shared" si="169"/>
-        <v>0.22887792655234507</v>
+        <f t="shared" si="182"/>
+        <v>0.12350450947910918</v>
       </c>
       <c r="AK42" s="8">
-        <f t="shared" si="169"/>
-        <v>-1</v>
+        <f t="shared" si="182"/>
+        <v>0.11491399184252526</v>
       </c>
       <c r="AL42" s="8">
-        <f t="shared" si="169"/>
-        <v>-1</v>
-      </c>
-      <c r="AM42" s="8"/>
-      <c r="AN42" s="8"/>
+        <f t="shared" si="182"/>
+        <v>0.140250260688217</v>
+      </c>
+      <c r="AM42" s="8">
+        <f t="shared" si="183"/>
+        <v>0.14613743064447293</v>
+      </c>
+      <c r="AN42" s="8">
+        <f t="shared" si="184"/>
+        <v>0.12467234600262134</v>
+      </c>
       <c r="AO42" s="8"/>
       <c r="AP42" s="8"/>
       <c r="BO42" s="13"/>
       <c r="BP42" s="13">
-        <f t="shared" ref="BP42" si="175">BP14/BO14-1</f>
+        <f t="shared" ref="BP42" si="190">BP14/BO14-1</f>
         <v>0.35596809486835612</v>
       </c>
       <c r="BQ42" s="13">
-        <f t="shared" ref="BQ42" si="176">BQ14/BP14-1</f>
+        <f t="shared" ref="BQ42" si="191">BQ14/BP14-1</f>
         <v>0.31218115564810001</v>
       </c>
       <c r="BR42" s="13">
@@ -7768,39 +8152,39 @@
         <v>0.26028484151227826</v>
       </c>
       <c r="BS42" s="13">
-        <f t="shared" ref="BS42:CA42" si="177">BS14/BR14-1</f>
+        <f t="shared" ref="BS42:CA42" si="192">BS14/BR14-1</f>
         <v>0.10859984890455809</v>
       </c>
       <c r="BT42" s="13">
-        <f t="shared" si="177"/>
+        <f t="shared" si="192"/>
         <v>0.14171730365154178</v>
       </c>
       <c r="BU42" s="13">
-        <f t="shared" si="177"/>
-        <v>0.39804521375811386</v>
+        <f t="shared" si="192"/>
+        <v>0.10358377477679137</v>
       </c>
       <c r="BV42" s="13">
-        <f t="shared" si="177"/>
+        <f t="shared" si="192"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="BW42" s="13">
-        <f t="shared" si="177"/>
+        <f t="shared" si="192"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="BX42" s="13">
-        <f t="shared" si="177"/>
+        <f t="shared" si="192"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="BY42" s="13">
-        <f t="shared" si="177"/>
+        <f t="shared" si="192"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="BZ42" s="13">
-        <f t="shared" si="177"/>
+        <f t="shared" si="192"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="CA42" s="13">
-        <f t="shared" si="177"/>
+        <f t="shared" si="192"/>
         <v>5.0000000000000044E-2</v>
       </c>
     </row>
@@ -7809,156 +8193,162 @@
         <v>59</v>
       </c>
       <c r="N43" s="8">
-        <f t="shared" si="173"/>
+        <f t="shared" si="188"/>
         <v>0.41145218417945695</v>
       </c>
       <c r="O43" s="8">
-        <f t="shared" si="173"/>
+        <f t="shared" si="188"/>
         <v>0.43814432989690721</v>
       </c>
       <c r="P43" s="8">
-        <f t="shared" si="173"/>
+        <f t="shared" si="188"/>
         <v>0.40606262491672229</v>
       </c>
       <c r="Q43" s="8">
-        <f t="shared" si="173"/>
+        <f t="shared" si="188"/>
         <v>0.50529838259899607</v>
       </c>
       <c r="R43" s="8">
-        <f t="shared" si="173"/>
+        <f t="shared" si="188"/>
         <v>0.53701380175658731</v>
       </c>
       <c r="S43" s="8">
-        <f t="shared" si="173"/>
+        <f t="shared" si="188"/>
         <v>0.63364055299539168</v>
       </c>
       <c r="T43" s="8">
-        <f t="shared" si="173"/>
+        <f t="shared" si="188"/>
         <v>0.76522151149016815</v>
       </c>
       <c r="U43" s="8">
-        <f t="shared" si="173"/>
+        <f t="shared" si="188"/>
         <v>0.41015190811411628</v>
       </c>
       <c r="V43" s="8">
-        <f t="shared" si="173"/>
+        <f t="shared" si="188"/>
         <v>0.32190476190476192</v>
       </c>
       <c r="W43" s="8">
-        <f t="shared" ref="W43" si="178">+W15/S15-1</f>
+        <f t="shared" ref="W43" si="193">+W15/S15-1</f>
         <v>0.23444601159692846</v>
       </c>
       <c r="X43" s="8">
-        <f t="shared" si="174"/>
+        <f t="shared" si="189"/>
         <v>0.17527848610924712</v>
       </c>
       <c r="Y43" s="8">
-        <f t="shared" si="174"/>
+        <f t="shared" si="189"/>
         <v>0.25433526011560703</v>
       </c>
       <c r="Z43" s="8">
-        <f t="shared" si="174"/>
+        <f t="shared" si="189"/>
         <v>0.18948126801152743</v>
       </c>
       <c r="AA43" s="8">
-        <f t="shared" si="174"/>
+        <f t="shared" si="189"/>
         <v>0.20718547670432907</v>
       </c>
       <c r="AB43" s="8">
-        <f t="shared" si="174"/>
+        <f t="shared" si="189"/>
         <v>0.21993833504624871</v>
       </c>
       <c r="AC43" s="8">
-        <f t="shared" si="174"/>
+        <f t="shared" si="189"/>
         <v>0.26309174696271476</v>
       </c>
       <c r="AD43" s="8">
-        <f t="shared" si="174"/>
+        <f t="shared" si="189"/>
         <v>0.26797611836981905</v>
       </c>
       <c r="AE43" s="8">
-        <f t="shared" si="169"/>
-        <v>0.12756336102639598</v>
+        <f t="shared" si="182"/>
+        <v>0.24345357030181924</v>
       </c>
       <c r="AF43" s="8">
-        <f t="shared" si="169"/>
-        <v>1.7130019657399576E-2</v>
+        <f t="shared" si="182"/>
+        <v>0.19545071609098574</v>
       </c>
       <c r="AG43" s="8">
-        <f t="shared" si="169"/>
-        <v>-6.4842454394693161E-2</v>
+        <f t="shared" si="182"/>
+        <v>0.18830845771144289</v>
       </c>
       <c r="AH43" s="8">
-        <f t="shared" si="169"/>
-        <v>-0.21468541012692777</v>
+        <f t="shared" si="182"/>
+        <v>0.17974614439743419</v>
       </c>
       <c r="AI43" s="8">
-        <f t="shared" si="169"/>
-        <v>9.2613318410744272E-2</v>
+        <f t="shared" si="182"/>
+        <v>0.17735115020297698</v>
       </c>
       <c r="AJ43" s="8">
-        <f t="shared" si="169"/>
-        <v>0.12350450947910918</v>
+        <f t="shared" si="182"/>
+        <v>0.22887792655234507</v>
       </c>
       <c r="AK43" s="8">
-        <f t="shared" si="169"/>
-        <v>-1</v>
+        <f t="shared" si="182"/>
+        <v>0.23529411764705888</v>
       </c>
       <c r="AL43" s="8">
-        <f t="shared" si="169"/>
-        <v>-1</v>
-      </c>
-      <c r="AM43" s="8"/>
-      <c r="AN43" s="8"/>
+        <f t="shared" si="182"/>
+        <v>0.23305182785747336</v>
+      </c>
+      <c r="AM43" s="8">
+        <f t="shared" si="183"/>
+        <v>0.23863228216363774</v>
+      </c>
+      <c r="AN43" s="8">
+        <f t="shared" si="184"/>
+        <v>0.26220211545813688</v>
+      </c>
       <c r="AO43" s="8"/>
       <c r="AP43" s="8"/>
       <c r="BO43" s="13"/>
       <c r="BP43" s="13">
-        <f t="shared" ref="BP43" si="179">BP15/BO15-1</f>
+        <f t="shared" ref="BP43" si="194">BP15/BO15-1</f>
         <v>0.39354966363276622</v>
       </c>
       <c r="BQ43" s="13">
-        <f t="shared" ref="BQ43:BR43" si="180">BQ15/BP15-1</f>
+        <f t="shared" ref="BQ43:BR43" si="195">BQ15/BP15-1</f>
         <v>0.4819679114013915</v>
       </c>
       <c r="BR43" s="13">
-        <f t="shared" si="180"/>
+        <f t="shared" si="195"/>
         <v>0.49269461077844312</v>
       </c>
       <c r="BS43" s="13">
-        <f t="shared" ref="BS43:CA43" si="181">BS15/BR15-1</f>
+        <f t="shared" ref="BS43:CA43" si="196">BS15/BR15-1</f>
         <v>0.21113607188703476</v>
       </c>
       <c r="BT43" s="13">
-        <f t="shared" si="181"/>
+        <f t="shared" si="196"/>
         <v>0.24290521741434601</v>
       </c>
       <c r="BU43" s="13">
-        <f t="shared" si="181"/>
-        <v>-5.3980301027587108E-2</v>
+        <f t="shared" si="196"/>
+        <v>0.19843943205560066</v>
       </c>
       <c r="BV43" s="13">
-        <f t="shared" si="181"/>
+        <f t="shared" si="196"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="BW43" s="13">
-        <f t="shared" si="181"/>
+        <f t="shared" si="196"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="BX43" s="13">
-        <f t="shared" si="181"/>
+        <f t="shared" si="196"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="BY43" s="13">
-        <f t="shared" si="181"/>
+        <f t="shared" si="196"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="BZ43" s="13">
-        <f t="shared" si="181"/>
+        <f t="shared" si="196"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="CA43" s="13">
-        <f t="shared" si="181"/>
+        <f t="shared" si="196"/>
         <v>5.0000000000000044E-2</v>
       </c>
     </row>
@@ -7967,71 +8357,71 @@
         <v>39</v>
       </c>
       <c r="N44" s="8">
-        <f t="shared" ref="N44:O44" si="182">N9/J9-1</f>
+        <f t="shared" ref="N44:O44" si="197">N9/J9-1</f>
         <v>0.33970390309555865</v>
       </c>
       <c r="O44" s="8">
-        <f t="shared" si="182"/>
+        <f t="shared" si="197"/>
         <v>0.32783264033264037</v>
       </c>
       <c r="P44" s="8">
-        <f t="shared" ref="P44" si="183">P9/L9-1</f>
+        <f t="shared" ref="P44" si="198">P9/L9-1</f>
         <v>0.28958358191146649</v>
       </c>
       <c r="Q44" s="8">
-        <f t="shared" ref="Q44" si="184">Q9/M9-1</f>
+        <f t="shared" ref="Q44" si="199">Q9/M9-1</f>
         <v>0.28971650917176217</v>
       </c>
       <c r="R44" s="8">
-        <f t="shared" ref="R44" si="185">R9/N9-1</f>
+        <f t="shared" ref="R44" si="200">R9/N9-1</f>
         <v>0.28008840667068524</v>
       </c>
       <c r="S44" s="8">
-        <f t="shared" ref="S44" si="186">S9/O9-1</f>
+        <f t="shared" ref="S44" si="201">S9/O9-1</f>
         <v>0.32136216850963883</v>
       </c>
       <c r="T44" s="8">
-        <f t="shared" ref="T44" si="187">T9/P9-1</f>
+        <f t="shared" ref="T44" si="202">T9/P9-1</f>
         <v>0.37018874907475952</v>
       </c>
       <c r="U44" s="8">
-        <f t="shared" ref="U44" si="188">U9/Q9-1</f>
+        <f t="shared" ref="U44" si="203">U9/Q9-1</f>
         <v>0.3886733902249806</v>
       </c>
       <c r="V44" s="8">
-        <f t="shared" ref="V44:AA44" si="189">V9/R9-1</f>
+        <f t="shared" ref="V44:AA44" si="204">V9/R9-1</f>
         <v>0.39538533982106427</v>
       </c>
       <c r="W44" s="8">
-        <f t="shared" si="189"/>
+        <f t="shared" si="204"/>
         <v>0.36569651188624741</v>
       </c>
       <c r="X44" s="8">
-        <f t="shared" si="189"/>
+        <f t="shared" si="204"/>
         <v>0.33290566547369838</v>
       </c>
       <c r="Y44" s="8">
-        <f t="shared" si="189"/>
+        <f t="shared" si="204"/>
         <v>0.27486033519553077</v>
       </c>
       <c r="Z44" s="8">
-        <f t="shared" si="189"/>
+        <f t="shared" si="204"/>
         <v>0.20236220472440936</v>
       </c>
       <c r="AA44" s="8">
-        <f t="shared" si="189"/>
+        <f t="shared" si="204"/>
         <v>0.157963234097934</v>
       </c>
       <c r="AB44" s="8">
-        <f t="shared" ref="AB44:AD44" si="190">AB9/X9-1</f>
+        <f t="shared" ref="AB44:AD44" si="205">AB9/X9-1</f>
         <v>0.12163736764780375</v>
       </c>
       <c r="AC44" s="8">
-        <f t="shared" si="190"/>
+        <f t="shared" si="205"/>
         <v>0.1227480767358069</v>
       </c>
       <c r="AD44" s="8">
-        <f t="shared" si="190"/>
+        <f t="shared" si="205"/>
         <v>0.13219197305641317</v>
       </c>
       <c r="AE44" s="8">
@@ -8043,55 +8433,61 @@
         <v>0.18703703703703711</v>
       </c>
       <c r="AG44" s="8">
-        <f t="shared" ref="AG44:AL44" si="191">AG9/AC9-1</f>
+        <f t="shared" ref="AG44:AL44" si="206">AG9/AC9-1</f>
         <v>0.1905112971074201</v>
       </c>
       <c r="AH44" s="8">
-        <f t="shared" si="191"/>
+        <f t="shared" si="206"/>
         <v>0.189307552470666</v>
       </c>
       <c r="AI44" s="8">
-        <f t="shared" si="191"/>
+        <f t="shared" si="206"/>
         <v>0.1689499540679793</v>
       </c>
       <c r="AJ44" s="8">
-        <f t="shared" si="191"/>
+        <f t="shared" si="206"/>
         <v>0.17472698907956308</v>
       </c>
       <c r="AK44" s="8">
-        <f t="shared" si="191"/>
-        <v>0.10000000000000009</v>
+        <f t="shared" si="206"/>
+        <v>0.20231677109135937</v>
       </c>
       <c r="AL44" s="8">
-        <f t="shared" si="191"/>
-        <v>0.10000000000000009</v>
-      </c>
-      <c r="AM44" s="8"/>
-      <c r="AN44" s="8"/>
+        <f t="shared" si="206"/>
+        <v>0.23598276940179264</v>
+      </c>
+      <c r="AM44" s="8">
+        <f t="shared" ref="AM44" si="207">AM9/AI9-1</f>
+        <v>0.28427922233231961</v>
+      </c>
+      <c r="AN44" s="8">
+        <f t="shared" ref="AN44" si="208">AN9/AJ9-1</f>
+        <v>0.36792666731448187</v>
+      </c>
       <c r="AO44" s="8"/>
       <c r="AP44" s="8"/>
       <c r="BL44" s="13">
-        <f t="shared" ref="BL44:BN44" si="192">BL9/BK9-1</f>
+        <f t="shared" ref="BL44:BN44" si="209">BL9/BK9-1</f>
         <v>0.69681309216192933</v>
       </c>
       <c r="BM44" s="13">
-        <f t="shared" si="192"/>
+        <f t="shared" si="209"/>
         <v>0.55063451776649752</v>
       </c>
       <c r="BN44" s="13">
-        <f t="shared" si="192"/>
+        <f t="shared" si="209"/>
         <v>0.42884033063262139</v>
       </c>
       <c r="BO44" s="13">
-        <f t="shared" ref="BO44" si="193">BO9/BN9-1</f>
+        <f t="shared" ref="BO44" si="210">BO9/BN9-1</f>
         <v>0.46944269431238905</v>
       </c>
       <c r="BP44" s="13">
-        <f t="shared" ref="BP44" si="194">BP9/BO9-1</f>
+        <f t="shared" ref="BP44" si="211">BP9/BO9-1</f>
         <v>0.36526992788930035</v>
       </c>
       <c r="BQ44" s="13">
-        <f t="shared" ref="BQ44" si="195">BQ9/BP9-1</f>
+        <f t="shared" ref="BQ44" si="212">BQ9/BP9-1</f>
         <v>0.29532347399074976</v>
       </c>
       <c r="BR44" s="13">
@@ -8099,39 +8495,39 @@
         <v>0.37099404893101173</v>
       </c>
       <c r="BS44" s="13">
-        <f t="shared" ref="BS44:CA44" si="196">BS9/BR9-1</f>
+        <f t="shared" ref="BS44:CA44" si="213">BS9/BR9-1</f>
         <v>0.28767563743931057</v>
       </c>
       <c r="BT44" s="13">
-        <f t="shared" si="196"/>
+        <f t="shared" si="213"/>
         <v>0.13310277666799841</v>
       </c>
       <c r="BU44" s="13">
-        <f t="shared" si="196"/>
+        <f t="shared" si="213"/>
         <v>0.18509867007503544</v>
       </c>
       <c r="BV44" s="13">
-        <f t="shared" si="196"/>
-        <v>0.13430956896872326</v>
+        <f t="shared" si="213"/>
+        <v>0.19681840157685304</v>
       </c>
       <c r="BW44" s="13">
-        <f t="shared" si="196"/>
+        <f t="shared" si="213"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="BX44" s="13">
-        <f t="shared" si="196"/>
+        <f t="shared" si="213"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="BY44" s="13">
-        <f t="shared" si="196"/>
+        <f t="shared" si="213"/>
         <v>0.14999999999999991</v>
       </c>
       <c r="BZ44" s="13">
-        <f t="shared" si="196"/>
+        <f t="shared" si="213"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="CA44" s="13">
-        <f t="shared" si="196"/>
+        <f t="shared" si="213"/>
         <v>0.10000000000000009</v>
       </c>
     </row>
@@ -8147,27 +8543,27 @@
       <c r="H45" s="16"/>
       <c r="I45" s="16"/>
       <c r="J45" s="16">
-        <f t="shared" ref="J45:O45" si="197">J23/J20</f>
+        <f t="shared" ref="J45:O45" si="214">J23/J20</f>
         <v>0.24272273876462705</v>
       </c>
       <c r="K45" s="16">
-        <f t="shared" si="197"/>
+        <f t="shared" si="214"/>
         <v>0.28775544388609714</v>
       </c>
       <c r="L45" s="16">
-        <f t="shared" si="197"/>
+        <f t="shared" si="214"/>
         <v>0.28067629802536115</v>
       </c>
       <c r="M45" s="16">
-        <f t="shared" si="197"/>
+        <f t="shared" si="214"/>
         <v>0.26452894357039769</v>
       </c>
       <c r="N45" s="16">
-        <f t="shared" si="197"/>
+        <f t="shared" si="214"/>
         <v>0.24323798849457323</v>
       </c>
       <c r="O45" s="16">
-        <f t="shared" si="197"/>
+        <f t="shared" si="214"/>
         <v>0.26061602078142393</v>
       </c>
       <c r="P45" s="16">
@@ -8187,11 +8583,11 @@
         <v>0.2726275825208721</v>
       </c>
       <c r="T45" s="16">
-        <f t="shared" ref="T45:W45" si="198">T23/T20</f>
+        <f t="shared" ref="T45:W45" si="215">T23/T20</f>
         <v>0.27649451715599577</v>
       </c>
       <c r="U45" s="16">
-        <f t="shared" si="198"/>
+        <f t="shared" si="215"/>
         <v>0.26516983720174708</v>
       </c>
       <c r="V45" s="16">
@@ -8199,11 +8595,11 @@
         <v>0.23383692836142403</v>
       </c>
       <c r="W45" s="16">
-        <f t="shared" si="198"/>
+        <f t="shared" si="215"/>
         <v>0.25483494211809971</v>
       </c>
       <c r="X45" s="16">
-        <f t="shared" ref="X45:AD45" si="199">X23/X20</f>
+        <f t="shared" ref="X45:AD45" si="216">X23/X20</f>
         <v>0.2843096821023805</v>
       </c>
       <c r="Y45" s="16">
@@ -8219,15 +8615,15 @@
         <v>0.30356946560090453</v>
       </c>
       <c r="AB45" s="16">
-        <f t="shared" si="199"/>
+        <f t="shared" si="216"/>
         <v>0.32522714926739243</v>
       </c>
       <c r="AC45" s="16">
-        <f t="shared" si="199"/>
+        <f t="shared" si="216"/>
         <v>0.3197235171194342</v>
       </c>
       <c r="AD45" s="16">
-        <f t="shared" si="199"/>
+        <f t="shared" si="216"/>
         <v>0.30191043827701647</v>
       </c>
       <c r="AE45" s="17">
@@ -8239,15 +8635,15 @@
         <v>0.3421251807701145</v>
       </c>
       <c r="AG45" s="16">
-        <f t="shared" ref="AG45:AL45" si="200">AG23/AG20</f>
+        <f t="shared" ref="AG45:AP45" si="217">AG23/AG20</f>
         <v>0.33510199714244354</v>
       </c>
       <c r="AH45" s="16">
-        <f t="shared" si="200"/>
+        <f t="shared" si="217"/>
         <v>0.32449199113913268</v>
       </c>
       <c r="AI45" s="16">
-        <f t="shared" si="200"/>
+        <f t="shared" si="217"/>
         <v>0.34752388110517962</v>
       </c>
       <c r="AJ45" s="16">
@@ -8255,43 +8651,55 @@
         <v>0.36324551883698464</v>
       </c>
       <c r="AK45" s="16">
-        <f t="shared" si="200"/>
+        <f t="shared" si="217"/>
+        <v>0.35422297953588022</v>
+      </c>
+      <c r="AL45" s="16">
+        <f t="shared" si="217"/>
+        <v>0.34023319243061867</v>
+      </c>
+      <c r="AM45" s="16">
+        <f t="shared" ref="AM45:AN45" si="218">AM23/AM20</f>
+        <v>0.36782375398718592</v>
+      </c>
+      <c r="AN45" s="16">
+        <f t="shared" si="218"/>
+        <v>0.37483923711155198</v>
+      </c>
+      <c r="AO45" s="16">
+        <f t="shared" si="217"/>
         <v>0.34</v>
       </c>
-      <c r="AL45" s="16">
-        <f t="shared" si="200"/>
+      <c r="AP45" s="16">
+        <f t="shared" si="217"/>
         <v>0.34</v>
       </c>
-      <c r="AM45" s="16"/>
-      <c r="AN45" s="16"/>
-      <c r="AO45" s="16"/>
-      <c r="AP45" s="16"/>
       <c r="BK45" s="14">
-        <f t="shared" ref="BK45:BM45" si="201">BK23/BK20</f>
+        <f t="shared" ref="BK45:BM45" si="219">BK23/BK20</f>
         <v>0.17384366431428958</v>
       </c>
       <c r="BL45" s="14">
-        <f t="shared" si="201"/>
+        <f t="shared" si="219"/>
         <v>0.20508195802104554</v>
       </c>
       <c r="BM45" s="14">
-        <f t="shared" si="201"/>
+        <f t="shared" si="219"/>
         <v>0.22136674829211617</v>
       </c>
       <c r="BN45" s="14">
-        <f t="shared" ref="BN45" si="202">BN23/BN20</f>
+        <f t="shared" ref="BN45" si="220">BN23/BN20</f>
         <v>0.22872836854710848</v>
       </c>
       <c r="BO45" s="14">
-        <f t="shared" ref="BO45:BP45" si="203">BO23/BO20</f>
+        <f t="shared" ref="BO45:BP45" si="221">BO23/BO20</f>
         <v>0.25636467471348767</v>
       </c>
       <c r="BP45" s="14">
-        <f t="shared" si="203"/>
+        <f t="shared" si="221"/>
         <v>0.26648533804835273</v>
       </c>
       <c r="BQ45" s="14">
-        <f t="shared" ref="BQ45" si="204">BQ23/BQ20</f>
+        <f t="shared" ref="BQ45" si="222">BQ23/BQ20</f>
         <v>0.24410719466202496</v>
       </c>
       <c r="BR45" s="14">
@@ -8299,40 +8707,40 @@
         <v>0.26045395915900066</v>
       </c>
       <c r="BS45" s="14">
-        <f t="shared" ref="BS45:CA45" si="205">BS23/BS20</f>
+        <f t="shared" ref="BS45:CA45" si="223">BS23/BS20</f>
         <v>0.27404213758042584</v>
       </c>
       <c r="BT45" s="14">
-        <f t="shared" si="205"/>
+        <f t="shared" si="223"/>
         <v>0.31216367859286515</v>
       </c>
       <c r="BU45" s="14">
-        <f t="shared" si="205"/>
+        <f t="shared" si="223"/>
         <v>0.28660196031406404</v>
       </c>
       <c r="BV45" s="14">
-        <f t="shared" si="205"/>
-        <v>0.29202550579581815</v>
+        <f t="shared" si="223"/>
+        <v>0.29210313119342013</v>
       </c>
       <c r="BW45" s="14">
-        <f t="shared" si="205"/>
-        <v>0.29750094367683211</v>
+        <f t="shared" si="223"/>
+        <v>0.29752782444330639</v>
       </c>
       <c r="BX45" s="14">
-        <f t="shared" si="205"/>
-        <v>0.3028656198769204</v>
+        <f t="shared" si="223"/>
+        <v>0.30283165458039746</v>
       </c>
       <c r="BY45" s="14">
-        <f t="shared" si="205"/>
-        <v>0.30280742244620346</v>
+        <f t="shared" si="223"/>
+        <v>0.30277174886234809</v>
       </c>
       <c r="BZ45" s="14">
-        <f t="shared" si="205"/>
-        <v>0.302776543093009</v>
+        <f t="shared" si="223"/>
+        <v>0.30274000513460958</v>
       </c>
       <c r="CA45" s="14">
-        <f t="shared" si="205"/>
-        <v>0.30274491358117539</v>
+        <f t="shared" si="223"/>
+        <v>0.30270752041121818</v>
       </c>
       <c r="CC45" t="s">
         <v>77</v>
@@ -8354,75 +8762,75 @@
         <v>75</v>
       </c>
       <c r="O47" s="4">
-        <f t="shared" ref="O47:P47" si="206">+O48-O61</f>
+        <f t="shared" ref="O47:P47" si="224">+O48-O61</f>
         <v>25855</v>
       </c>
       <c r="P47" s="4">
-        <f t="shared" si="206"/>
+        <f t="shared" si="224"/>
         <v>38263</v>
       </c>
       <c r="Q47" s="4">
-        <f t="shared" ref="Q47" si="207">+Q48-Q61</f>
+        <f t="shared" ref="Q47" si="225">+Q48-Q61</f>
         <v>35473</v>
       </c>
       <c r="R47" s="4">
-        <f t="shared" ref="R47:AB47" si="208">+R48-R61</f>
+        <f t="shared" ref="R47:AB47" si="226">+R48-R61</f>
         <v>52580</v>
       </c>
       <c r="S47" s="4">
-        <f t="shared" si="208"/>
+        <f t="shared" si="226"/>
         <v>41402</v>
       </c>
       <c r="T47" s="4">
-        <f t="shared" si="208"/>
+        <f t="shared" si="226"/>
         <v>39615</v>
       </c>
       <c r="U47" s="4">
-        <f t="shared" si="208"/>
+        <f t="shared" si="226"/>
         <v>28933</v>
       </c>
       <c r="V47" s="4">
-        <f t="shared" si="208"/>
+        <f t="shared" si="226"/>
         <v>47305</v>
       </c>
       <c r="W47" s="4">
-        <f t="shared" si="208"/>
+        <f t="shared" si="226"/>
         <v>18829</v>
       </c>
       <c r="X47" s="4">
-        <f t="shared" si="208"/>
+        <f t="shared" si="226"/>
         <v>2657</v>
       </c>
       <c r="Y47" s="4">
-        <f t="shared" si="208"/>
+        <f t="shared" si="226"/>
         <v>-257</v>
       </c>
       <c r="Z47" s="4">
-        <f t="shared" si="208"/>
+        <f t="shared" si="226"/>
         <v>2876</v>
       </c>
       <c r="AA47" s="4">
-        <f t="shared" si="208"/>
+        <f t="shared" si="226"/>
         <v>-2679</v>
       </c>
       <c r="AB47" s="4">
-        <f t="shared" si="208"/>
+        <f t="shared" si="226"/>
         <v>878</v>
       </c>
       <c r="AC47" s="4">
-        <f t="shared" ref="AC47:AD47" si="209">+AC48-AC61</f>
+        <f t="shared" ref="AC47:AD47" si="227">+AC48-AC61</f>
         <v>3071</v>
       </c>
       <c r="AD47" s="4">
-        <f t="shared" si="209"/>
+        <f t="shared" si="227"/>
         <v>28466</v>
       </c>
       <c r="AE47" s="4">
-        <f t="shared" ref="AE47:AF47" si="210">+AE48-AE61</f>
+        <f t="shared" ref="AE47:AF47" si="228">+AE48-AE61</f>
         <v>27440</v>
       </c>
       <c r="AF47" s="4">
-        <f t="shared" si="210"/>
+        <f t="shared" si="228"/>
         <v>34203</v>
       </c>
       <c r="AG47" s="4">
@@ -8464,28 +8872,28 @@
         <v>48579</v>
       </c>
       <c r="BV47" s="2">
-        <f t="shared" ref="BV47:CA47" si="211">+BU47+BV32</f>
-        <v>90886.728130000018</v>
+        <f t="shared" ref="BV47:CA47" si="229">+BU47+BV32</f>
+        <v>92601.144129999986</v>
       </c>
       <c r="BW47" s="2">
-        <f t="shared" si="211"/>
-        <v>147575.41995300498</v>
+        <f t="shared" si="229"/>
+        <v>151361.70768900498</v>
       </c>
       <c r="BX47" s="2">
-        <f t="shared" si="211"/>
-        <v>220948.67022527254</v>
+        <f t="shared" si="229"/>
+        <v>227235.90044702846</v>
       </c>
       <c r="BY47" s="2">
-        <f t="shared" si="211"/>
-        <v>305744.74678757193</v>
+        <f t="shared" si="229"/>
+        <v>314924.49136221269</v>
       </c>
       <c r="BZ47" s="2">
-        <f t="shared" si="211"/>
-        <v>400778.14039390185</v>
+        <f t="shared" si="229"/>
+        <v>413158.89298302698</v>
       </c>
       <c r="CA47" s="2">
-        <f t="shared" si="211"/>
-        <v>506953.13147166232</v>
+        <f t="shared" si="229"/>
+        <v>522874.39866195503</v>
       </c>
       <c r="CC47" t="s">
         <v>78</v>
@@ -8615,7 +9023,7 @@
       </c>
       <c r="CD48" s="2">
         <f>NPV(CD45,BV32:EM32)+Main!K5-Main!K6</f>
-        <v>1211669.1413828339</v>
+        <v>1251206.8740880571</v>
       </c>
     </row>
     <row r="49" spans="2:82" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8701,20 +9109,20 @@
         <v>57415</v>
       </c>
       <c r="BS49" s="2">
-        <f t="shared" ref="BS49:BS54" si="212">+Z49</f>
+        <f t="shared" ref="BS49:BS54" si="230">+Z49</f>
         <v>34405</v>
       </c>
       <c r="BT49" s="2">
-        <f t="shared" ref="BT49:BT54" si="213">+AD49</f>
+        <f t="shared" ref="BT49:BT54" si="231">+AD49</f>
         <v>33318</v>
       </c>
       <c r="BU49" s="2">
-        <f t="shared" ref="BU49:BU54" si="214">+AH49</f>
+        <f t="shared" ref="BU49:BU54" si="232">+AH49</f>
         <v>34214</v>
       </c>
       <c r="CD49" s="1">
         <f>+CD48/Main!K3</f>
-        <v>112.12929311334759</v>
+        <v>115.06408626890354</v>
       </c>
     </row>
     <row r="50" spans="2:82" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8800,15 +9208,15 @@
         <v>40825</v>
       </c>
       <c r="BS50" s="2">
-        <f t="shared" si="212"/>
+        <f t="shared" si="230"/>
         <v>42360</v>
       </c>
       <c r="BT50" s="2">
-        <f t="shared" si="213"/>
+        <f t="shared" si="231"/>
         <v>52253</v>
       </c>
       <c r="BU50" s="2">
-        <f t="shared" si="214"/>
+        <f t="shared" si="232"/>
         <v>55451</v>
       </c>
     </row>
@@ -8895,15 +9303,15 @@
         <v>297616</v>
       </c>
       <c r="BS51" s="2">
-        <f t="shared" si="212"/>
+        <f t="shared" si="230"/>
         <v>186715</v>
       </c>
       <c r="BT51" s="2">
-        <f t="shared" si="213"/>
+        <f t="shared" si="231"/>
         <v>204177</v>
       </c>
       <c r="BU51" s="2">
-        <f t="shared" si="214"/>
+        <f t="shared" si="232"/>
         <v>252665</v>
       </c>
     </row>
@@ -8990,15 +9398,15 @@
         <v>82125</v>
       </c>
       <c r="BS52" s="2">
-        <f t="shared" si="212"/>
+        <f t="shared" si="230"/>
         <v>66123</v>
       </c>
       <c r="BT52" s="2">
-        <f t="shared" si="213"/>
+        <f t="shared" si="231"/>
         <v>72513</v>
       </c>
       <c r="BU52" s="2">
-        <f t="shared" si="214"/>
+        <f t="shared" si="232"/>
         <v>76141</v>
       </c>
     </row>
@@ -9086,15 +9494,15 @@
         <v>23155</v>
       </c>
       <c r="BS53" s="2">
-        <f t="shared" si="212"/>
+        <f t="shared" si="230"/>
         <v>20288</v>
       </c>
       <c r="BT53" s="2">
-        <f t="shared" si="213"/>
+        <f t="shared" si="231"/>
         <v>22789</v>
       </c>
       <c r="BU53" s="2">
-        <f t="shared" si="214"/>
+        <f t="shared" si="232"/>
         <v>23074</v>
       </c>
     </row>
@@ -9181,15 +9589,15 @@
         <v>87854</v>
       </c>
       <c r="BS54" s="2">
-        <f t="shared" si="212"/>
+        <f t="shared" si="230"/>
         <v>42758</v>
       </c>
       <c r="BT54" s="2">
-        <f t="shared" si="213"/>
+        <f t="shared" si="231"/>
         <v>56024</v>
       </c>
       <c r="BU54" s="2">
-        <f t="shared" si="214"/>
+        <f t="shared" si="232"/>
         <v>82147</v>
       </c>
     </row>
@@ -9210,91 +9618,91 @@
       <c r="M55" s="4"/>
       <c r="N55" s="4"/>
       <c r="O55" s="4">
-        <f t="shared" ref="O55:P55" si="215">SUM(O48:O54)</f>
+        <f t="shared" ref="O55:P55" si="233">SUM(O48:O54)</f>
         <v>221238</v>
       </c>
       <c r="P55" s="4">
-        <f t="shared" si="215"/>
+        <f t="shared" si="233"/>
         <v>258314</v>
       </c>
       <c r="Q55" s="4">
-        <f t="shared" ref="Q55" si="216">SUM(Q48:Q54)</f>
+        <f t="shared" ref="Q55" si="234">SUM(Q48:Q54)</f>
         <v>282179</v>
       </c>
       <c r="R55" s="4">
-        <f t="shared" ref="R55:AB55" si="217">SUM(R48:R54)</f>
+        <f t="shared" ref="R55:AB55" si="235">SUM(R48:R54)</f>
         <v>321195</v>
       </c>
       <c r="S55" s="4">
-        <f t="shared" si="217"/>
+        <f t="shared" si="235"/>
         <v>323077</v>
       </c>
       <c r="T55" s="4">
-        <f t="shared" si="217"/>
+        <f t="shared" si="235"/>
         <v>360319</v>
       </c>
       <c r="U55" s="4">
-        <f t="shared" si="217"/>
+        <f t="shared" si="235"/>
         <v>382406</v>
       </c>
       <c r="V55" s="4">
-        <f t="shared" si="217"/>
+        <f t="shared" si="235"/>
         <v>420549</v>
       </c>
       <c r="W55" s="4">
-        <f t="shared" si="217"/>
+        <f t="shared" si="235"/>
         <v>410767</v>
       </c>
       <c r="X55" s="4">
-        <f t="shared" si="217"/>
+        <f t="shared" si="235"/>
         <v>419728</v>
       </c>
       <c r="Y55" s="4">
-        <f t="shared" si="217"/>
+        <f t="shared" si="235"/>
         <v>428362</v>
       </c>
       <c r="Z55" s="4">
-        <f t="shared" si="217"/>
+        <f t="shared" si="235"/>
         <v>462675</v>
       </c>
       <c r="AA55" s="4">
-        <f t="shared" si="217"/>
+        <f t="shared" si="235"/>
         <v>464378</v>
       </c>
       <c r="AB55" s="4">
-        <f t="shared" si="217"/>
+        <f t="shared" si="235"/>
         <v>477607</v>
       </c>
       <c r="AC55" s="4">
-        <f t="shared" ref="AC55:AD55" si="218">SUM(AC48:AC54)</f>
+        <f t="shared" ref="AC55:AD55" si="236">SUM(AC48:AC54)</f>
         <v>486883</v>
       </c>
       <c r="AD55" s="4">
-        <f t="shared" si="218"/>
+        <f t="shared" si="236"/>
         <v>527854</v>
       </c>
       <c r="AE55" s="4">
-        <f t="shared" ref="AE55:AJ55" si="219">SUM(AE48:AE54)</f>
+        <f t="shared" ref="AE55:AJ55" si="237">SUM(AE48:AE54)</f>
         <v>530969</v>
       </c>
       <c r="AF55" s="4">
-        <f t="shared" si="219"/>
+        <f t="shared" si="237"/>
         <v>554818</v>
       </c>
       <c r="AG55" s="4">
-        <f t="shared" si="219"/>
+        <f t="shared" si="237"/>
         <v>584626</v>
       </c>
       <c r="AH55" s="4">
-        <f t="shared" si="219"/>
+        <f t="shared" si="237"/>
         <v>624894</v>
       </c>
       <c r="AI55" s="4">
-        <f t="shared" si="219"/>
+        <f t="shared" si="237"/>
         <v>643256</v>
       </c>
       <c r="AJ55" s="4">
-        <f t="shared" si="219"/>
+        <f t="shared" si="237"/>
         <v>682170</v>
       </c>
       <c r="BS55" s="2">
@@ -9393,15 +9801,15 @@
         <v>98285</v>
       </c>
       <c r="BS57" s="2">
-        <f t="shared" ref="BS57:BS63" si="220">+Z57</f>
+        <f t="shared" ref="BS57:BS63" si="238">+Z57</f>
         <v>79600</v>
       </c>
       <c r="BT57" s="2">
-        <f t="shared" ref="BT57:BT63" si="221">+AD57</f>
+        <f t="shared" ref="BT57:BT63" si="239">+AD57</f>
         <v>84981</v>
       </c>
       <c r="BU57" s="2">
-        <f t="shared" ref="BU57:BU63" si="222">+AH57</f>
+        <f t="shared" ref="BU57:BU63" si="240">+AH57</f>
         <v>94363</v>
       </c>
     </row>
@@ -9488,15 +9896,15 @@
         <v>66974</v>
       </c>
       <c r="BS58" s="2">
-        <f t="shared" si="220"/>
+        <f t="shared" si="238"/>
         <v>62566</v>
       </c>
       <c r="BT58" s="2">
-        <f t="shared" si="221"/>
+        <f t="shared" si="239"/>
         <v>64709</v>
       </c>
       <c r="BU58" s="2">
-        <f t="shared" si="222"/>
+        <f t="shared" si="240"/>
         <v>66965</v>
       </c>
     </row>
@@ -9583,15 +9991,15 @@
         <v>21662</v>
       </c>
       <c r="BS59" s="2">
-        <f t="shared" si="220"/>
+        <f t="shared" si="238"/>
         <v>13227</v>
       </c>
       <c r="BT59" s="2">
-        <f t="shared" si="221"/>
+        <f t="shared" si="239"/>
         <v>15227</v>
       </c>
       <c r="BU59" s="2">
-        <f t="shared" si="222"/>
+        <f t="shared" si="240"/>
         <v>18103</v>
       </c>
     </row>
@@ -9678,15 +10086,15 @@
         <v>83221</v>
       </c>
       <c r="BS60" s="2">
-        <f t="shared" si="220"/>
+        <f t="shared" si="238"/>
         <v>72968</v>
       </c>
       <c r="BT60" s="2">
-        <f t="shared" si="221"/>
+        <f t="shared" si="239"/>
         <v>77297</v>
       </c>
       <c r="BU60" s="2">
-        <f t="shared" si="222"/>
+        <f t="shared" si="240"/>
         <v>78277</v>
       </c>
     </row>
@@ -9773,15 +10181,15 @@
         <v>50718</v>
       </c>
       <c r="BS61" s="2">
-        <f t="shared" si="220"/>
+        <f t="shared" si="238"/>
         <v>67150</v>
       </c>
       <c r="BT61" s="2">
-        <f t="shared" si="221"/>
+        <f t="shared" si="239"/>
         <v>58314</v>
       </c>
       <c r="BU61" s="2">
-        <f t="shared" si="222"/>
+        <f t="shared" si="240"/>
         <v>52623</v>
       </c>
     </row>
@@ -9868,15 +10276,15 @@
         <v>27535</v>
       </c>
       <c r="BS62" s="2">
-        <f t="shared" si="220"/>
+        <f t="shared" si="238"/>
         <v>21121</v>
       </c>
       <c r="BT62" s="2">
-        <f t="shared" si="221"/>
+        <f t="shared" si="239"/>
         <v>25451</v>
       </c>
       <c r="BU62" s="2">
-        <f t="shared" si="222"/>
+        <f t="shared" si="240"/>
         <v>28593</v>
       </c>
     </row>
@@ -9963,15 +10371,15 @@
         <v>333775</v>
       </c>
       <c r="BS63" s="2">
-        <f t="shared" si="220"/>
+        <f t="shared" si="238"/>
         <v>146043</v>
       </c>
       <c r="BT63" s="2">
-        <f t="shared" si="221"/>
+        <f t="shared" si="239"/>
         <v>201875</v>
       </c>
       <c r="BU63" s="2">
-        <f t="shared" si="222"/>
+        <f t="shared" si="240"/>
         <v>285970</v>
       </c>
     </row>
@@ -9992,71 +10400,71 @@
       <c r="M64" s="4"/>
       <c r="N64" s="4"/>
       <c r="O64" s="4">
-        <f t="shared" ref="O64:P64" si="223">SUM(O57:O63)</f>
+        <f t="shared" ref="O64:P64" si="241">SUM(O57:O63)</f>
         <v>221238</v>
       </c>
       <c r="P64" s="4">
-        <f t="shared" si="223"/>
+        <f t="shared" si="241"/>
         <v>258314</v>
       </c>
       <c r="Q64" s="4">
-        <f t="shared" ref="Q64" si="224">SUM(Q57:Q63)</f>
+        <f t="shared" ref="Q64" si="242">SUM(Q57:Q63)</f>
         <v>282179</v>
       </c>
       <c r="R64" s="4">
-        <f t="shared" ref="R64:AB64" si="225">SUM(R57:R63)</f>
+        <f t="shared" ref="R64:AB64" si="243">SUM(R57:R63)</f>
         <v>321195</v>
       </c>
       <c r="S64" s="4">
-        <f t="shared" si="225"/>
+        <f t="shared" si="243"/>
         <v>323077</v>
       </c>
       <c r="T64" s="4">
-        <f t="shared" si="225"/>
+        <f t="shared" si="243"/>
         <v>360319</v>
       </c>
       <c r="U64" s="4">
-        <f t="shared" si="225"/>
+        <f t="shared" si="243"/>
         <v>382406</v>
       </c>
       <c r="V64" s="4">
-        <f t="shared" si="225"/>
+        <f t="shared" si="243"/>
         <v>420549</v>
       </c>
       <c r="W64" s="4">
-        <f t="shared" si="225"/>
+        <f t="shared" si="243"/>
         <v>410767</v>
       </c>
       <c r="X64" s="4">
-        <f t="shared" si="225"/>
+        <f t="shared" si="243"/>
         <v>419728</v>
       </c>
       <c r="Y64" s="4">
-        <f t="shared" si="225"/>
+        <f t="shared" si="243"/>
         <v>428362</v>
       </c>
       <c r="Z64" s="4">
-        <f t="shared" si="225"/>
+        <f t="shared" si="243"/>
         <v>462675</v>
       </c>
       <c r="AA64" s="4">
-        <f t="shared" si="225"/>
+        <f t="shared" si="243"/>
         <v>464378</v>
       </c>
       <c r="AB64" s="4">
-        <f t="shared" si="225"/>
+        <f t="shared" si="243"/>
         <v>477607</v>
       </c>
       <c r="AC64" s="4">
-        <f t="shared" ref="AC64:AD64" si="226">SUM(AC57:AC63)</f>
+        <f t="shared" ref="AC64:AD64" si="244">SUM(AC57:AC63)</f>
         <v>486883</v>
       </c>
       <c r="AD64" s="4">
-        <f t="shared" si="226"/>
+        <f t="shared" si="244"/>
         <v>527854</v>
       </c>
       <c r="AE64" s="4">
-        <f t="shared" ref="AE64" si="227">SUM(AE57:AE63)</f>
+        <f t="shared" ref="AE64" si="245">SUM(AE57:AE63)</f>
         <v>530969</v>
       </c>
       <c r="AF64" s="4">
@@ -10109,71 +10517,71 @@
       <c r="M66" s="4"/>
       <c r="N66" s="4"/>
       <c r="O66" s="4">
-        <f t="shared" ref="O66:Q66" si="228">+O32</f>
+        <f t="shared" ref="O66:Q66" si="246">+O32</f>
         <v>2535</v>
       </c>
       <c r="P66" s="4">
-        <f t="shared" si="228"/>
+        <f t="shared" si="246"/>
         <v>5243</v>
       </c>
       <c r="Q66" s="4">
-        <f t="shared" si="228"/>
+        <f t="shared" si="246"/>
         <v>6331</v>
       </c>
       <c r="R66" s="4">
-        <f t="shared" ref="R66:V66" si="229">+R32</f>
+        <f t="shared" ref="R66:V66" si="247">+R32</f>
         <v>7222</v>
       </c>
       <c r="S66" s="4">
-        <f t="shared" si="229"/>
+        <f t="shared" si="247"/>
         <v>8107</v>
       </c>
       <c r="T66" s="4">
-        <f t="shared" si="229"/>
+        <f t="shared" si="247"/>
         <v>7778</v>
       </c>
       <c r="U66" s="4">
-        <f t="shared" si="229"/>
+        <f t="shared" si="247"/>
         <v>3156</v>
       </c>
       <c r="V66" s="4">
-        <f t="shared" si="229"/>
+        <f t="shared" si="247"/>
         <v>14323</v>
       </c>
       <c r="W66" s="4">
-        <f t="shared" ref="W66:AE66" si="230">+W32</f>
+        <f t="shared" ref="W66:AE66" si="248">+W32</f>
         <v>-3844</v>
       </c>
       <c r="X66" s="4">
-        <f t="shared" si="230"/>
+        <f t="shared" si="248"/>
         <v>2982</v>
       </c>
       <c r="Y66" s="4">
-        <f t="shared" si="230"/>
+        <f t="shared" si="248"/>
         <v>2872</v>
       </c>
       <c r="Z66" s="4">
-        <f t="shared" si="230"/>
+        <f t="shared" si="248"/>
         <v>3247</v>
       </c>
       <c r="AA66" s="4">
-        <f t="shared" si="230"/>
+        <f t="shared" si="248"/>
         <v>3172</v>
       </c>
       <c r="AB66" s="4">
-        <f t="shared" si="230"/>
+        <f t="shared" si="248"/>
         <v>6750</v>
       </c>
       <c r="AC66" s="4">
-        <f t="shared" si="230"/>
+        <f t="shared" si="248"/>
         <v>9879</v>
       </c>
       <c r="AD66" s="4">
-        <f t="shared" si="230"/>
+        <f t="shared" si="248"/>
         <v>10624</v>
       </c>
       <c r="AE66" s="4">
-        <f t="shared" si="230"/>
+        <f t="shared" si="248"/>
         <v>10431</v>
       </c>
       <c r="AF66" s="4">
@@ -10296,7 +10704,7 @@
         <v>-2722</v>
       </c>
       <c r="BT67" s="2">
-        <f t="shared" ref="BT67:BT73" si="231">SUM(AA67:AD67)</f>
+        <f t="shared" ref="BT67:BT73" si="249">SUM(AA67:AD67)</f>
         <v>30425</v>
       </c>
       <c r="BU67" s="2">
@@ -10387,15 +10795,15 @@
         <v>15227</v>
       </c>
       <c r="BS68" s="2">
-        <f t="shared" ref="BS68:BS73" si="232">SUM(W68:Z68)</f>
+        <f t="shared" ref="BS68:BS73" si="250">SUM(W68:Z68)</f>
         <v>41461</v>
       </c>
       <c r="BT68" s="2">
-        <f t="shared" si="231"/>
+        <f t="shared" si="249"/>
         <v>48663</v>
       </c>
       <c r="BU68" s="2">
-        <f t="shared" ref="BU68:BU72" si="233">SUM(AE68:AH68)</f>
+        <f t="shared" ref="BU68:BU72" si="251">SUM(AE68:AH68)</f>
         <v>52795</v>
       </c>
     </row>
@@ -10482,15 +10890,15 @@
         <v>6534</v>
       </c>
       <c r="BS69" s="2">
-        <f t="shared" si="232"/>
+        <f t="shared" si="250"/>
         <v>19621</v>
       </c>
       <c r="BT69" s="2">
-        <f t="shared" si="231"/>
+        <f t="shared" si="249"/>
         <v>24023</v>
       </c>
       <c r="BU69" s="2">
-        <f t="shared" si="233"/>
+        <f t="shared" si="251"/>
         <v>22011</v>
       </c>
     </row>
@@ -10577,15 +10985,15 @@
         <v>-1258</v>
       </c>
       <c r="BS70" s="2">
-        <f t="shared" si="232"/>
+        <f t="shared" si="250"/>
         <v>3905</v>
       </c>
       <c r="BT70" s="2">
-        <f t="shared" si="231"/>
+        <f t="shared" si="249"/>
         <v>-748</v>
       </c>
       <c r="BU70" s="2">
-        <f t="shared" si="233"/>
+        <f t="shared" si="251"/>
         <v>2012</v>
       </c>
     </row>
@@ -10654,15 +11062,15 @@
         <v>0</v>
       </c>
       <c r="BS71" s="2">
-        <f t="shared" si="232"/>
+        <f t="shared" si="250"/>
         <v>13521</v>
       </c>
       <c r="BT71" s="2">
-        <f t="shared" si="231"/>
+        <f t="shared" si="249"/>
         <v>0</v>
       </c>
       <c r="BU71" s="2">
-        <f t="shared" si="233"/>
+        <f t="shared" si="251"/>
         <v>0</v>
       </c>
     </row>
@@ -10749,15 +11157,15 @@
         <v>11</v>
       </c>
       <c r="BS72" s="2">
-        <f t="shared" si="232"/>
+        <f t="shared" si="250"/>
         <v>-8148</v>
       </c>
       <c r="BT72" s="2">
-        <f t="shared" si="231"/>
+        <f t="shared" si="249"/>
         <v>-5876</v>
       </c>
       <c r="BU72" s="2">
-        <f t="shared" si="233"/>
+        <f t="shared" si="251"/>
         <v>-4648</v>
       </c>
     </row>
@@ -10866,11 +11274,11 @@
         <v>-6163</v>
       </c>
       <c r="BS73" s="2">
-        <f t="shared" si="232"/>
+        <f t="shared" si="250"/>
         <v>-20886</v>
       </c>
       <c r="BT73" s="2">
-        <f t="shared" si="231"/>
+        <f t="shared" si="249"/>
         <v>-11541</v>
       </c>
       <c r="BU73" s="2">
@@ -10895,91 +11303,91 @@
       <c r="M74" s="4"/>
       <c r="N74" s="4"/>
       <c r="O74" s="4">
-        <f t="shared" ref="O74:Q74" si="234">SUM(O67:O73)</f>
+        <f t="shared" ref="O74:Q74" si="252">SUM(O67:O73)</f>
         <v>3064</v>
       </c>
       <c r="P74" s="4">
-        <f t="shared" si="234"/>
+        <f t="shared" si="252"/>
         <v>20606</v>
       </c>
       <c r="Q74" s="4">
-        <f t="shared" si="234"/>
+        <f t="shared" si="252"/>
         <v>11964</v>
       </c>
       <c r="R74" s="4">
-        <f t="shared" ref="R74:AJ74" si="235">SUM(R67:R73)</f>
+        <f t="shared" ref="R74:AJ74" si="253">SUM(R67:R73)</f>
         <v>30430</v>
       </c>
       <c r="S74" s="4">
-        <f t="shared" si="235"/>
+        <f t="shared" si="253"/>
         <v>4213</v>
       </c>
       <c r="T74" s="4">
-        <f t="shared" si="235"/>
+        <f t="shared" si="253"/>
         <v>12715</v>
       </c>
       <c r="U74" s="4">
-        <f t="shared" si="235"/>
+        <f t="shared" si="253"/>
         <v>7313</v>
       </c>
       <c r="V74" s="4">
-        <f t="shared" si="235"/>
+        <f t="shared" si="253"/>
         <v>22086</v>
       </c>
       <c r="W74" s="4">
-        <f t="shared" si="235"/>
+        <f t="shared" si="253"/>
         <v>-2790</v>
       </c>
       <c r="X74" s="4">
-        <f t="shared" si="235"/>
+        <f t="shared" si="253"/>
         <v>8965</v>
       </c>
       <c r="Y74" s="4">
-        <f t="shared" si="235"/>
+        <f t="shared" si="253"/>
         <v>11404</v>
       </c>
       <c r="Z74" s="4">
-        <f t="shared" si="235"/>
+        <f t="shared" si="253"/>
         <v>29173</v>
       </c>
       <c r="AA74" s="4">
-        <f t="shared" si="235"/>
+        <f t="shared" si="253"/>
         <v>4788</v>
       </c>
       <c r="AB74" s="4">
-        <f t="shared" si="235"/>
+        <f t="shared" si="253"/>
         <v>16476</v>
       </c>
       <c r="AC74" s="4">
-        <f t="shared" si="235"/>
+        <f t="shared" si="253"/>
         <v>21217</v>
       </c>
       <c r="AD74" s="4">
-        <f t="shared" si="235"/>
+        <f t="shared" si="253"/>
         <v>42465</v>
       </c>
       <c r="AE74" s="4">
-        <f t="shared" si="235"/>
+        <f t="shared" si="253"/>
         <v>18989</v>
       </c>
       <c r="AF74" s="4">
-        <f t="shared" si="235"/>
+        <f t="shared" si="253"/>
         <v>25281</v>
       </c>
       <c r="AG74" s="4">
-        <f t="shared" si="235"/>
+        <f t="shared" si="253"/>
         <v>25971</v>
       </c>
       <c r="AH74" s="4">
-        <f t="shared" si="235"/>
+        <f t="shared" si="253"/>
         <v>45636</v>
       </c>
       <c r="AI74" s="4">
-        <f t="shared" si="235"/>
+        <f t="shared" si="253"/>
         <v>17015</v>
       </c>
       <c r="AJ74" s="4">
-        <f t="shared" si="235"/>
+        <f t="shared" si="253"/>
         <v>32515</v>
       </c>
       <c r="AX74" s="2">
@@ -11121,7 +11529,7 @@
         <v>-32183</v>
       </c>
       <c r="BS76" s="2">
-        <f t="shared" ref="BS76:BS79" si="236">SUM(W76:Z76)</f>
+        <f t="shared" ref="BS76:BS79" si="254">SUM(W76:Z76)</f>
         <v>-63645</v>
       </c>
       <c r="BT76" s="2">
@@ -11129,7 +11537,7 @@
         <v>-52729</v>
       </c>
       <c r="BU76" s="2">
-        <f t="shared" ref="BU76:BU79" si="237">SUM(AE76:AH76)</f>
+        <f t="shared" ref="BU76:BU79" si="255">SUM(AE76:AH76)</f>
         <v>-82999</v>
       </c>
       <c r="BV76" s="2">
@@ -11220,15 +11628,15 @@
         <v>815</v>
       </c>
       <c r="BS77" s="2">
-        <f t="shared" si="236"/>
+        <f t="shared" si="254"/>
         <v>5324</v>
       </c>
       <c r="BT77" s="2">
-        <f t="shared" ref="BT77:BT79" si="238">SUM(AA77:AD77)</f>
+        <f t="shared" ref="BT77:BT79" si="256">SUM(AA77:AD77)</f>
         <v>4596</v>
       </c>
       <c r="BU77" s="2">
-        <f t="shared" si="237"/>
+        <f t="shared" si="255"/>
         <v>5341</v>
       </c>
     </row>
@@ -11315,15 +11723,15 @@
         <v>-1700</v>
       </c>
       <c r="BS78" s="2">
-        <f t="shared" si="236"/>
+        <f t="shared" si="254"/>
         <v>-8316</v>
       </c>
       <c r="BT78" s="2">
-        <f t="shared" si="238"/>
+        <f t="shared" si="256"/>
         <v>-5839</v>
       </c>
       <c r="BU78" s="2">
-        <f t="shared" si="237"/>
+        <f t="shared" si="255"/>
         <v>-7082</v>
       </c>
     </row>
@@ -11432,15 +11840,15 @@
         <v>-6356</v>
       </c>
       <c r="BS79" s="2">
-        <f t="shared" si="236"/>
+        <f t="shared" si="254"/>
         <v>29036</v>
       </c>
       <c r="BT79" s="2">
-        <f t="shared" si="238"/>
+        <f t="shared" si="256"/>
         <v>4139</v>
       </c>
       <c r="BU79" s="2">
-        <f t="shared" si="237"/>
+        <f t="shared" si="255"/>
         <v>-9602</v>
       </c>
     </row>
@@ -11461,91 +11869,91 @@
       <c r="M80" s="4"/>
       <c r="N80" s="4"/>
       <c r="O80" s="4">
-        <f t="shared" ref="O80:Q80" si="239">SUM(O76:O79)</f>
+        <f t="shared" ref="O80:Q80" si="257">SUM(O76:O79)</f>
         <v>-8894</v>
       </c>
       <c r="P80" s="4">
-        <f t="shared" si="239"/>
+        <f t="shared" si="257"/>
         <v>-17804</v>
       </c>
       <c r="Q80" s="4">
-        <f t="shared" si="239"/>
+        <f t="shared" si="257"/>
         <v>-15876</v>
       </c>
       <c r="R80" s="4">
-        <f t="shared" ref="R80:AJ80" si="240">SUM(R76:R79)</f>
+        <f t="shared" ref="R80:AJ80" si="258">SUM(R76:R79)</f>
         <v>-17038</v>
       </c>
       <c r="S80" s="4">
-        <f t="shared" si="240"/>
+        <f t="shared" si="258"/>
         <v>-8666</v>
       </c>
       <c r="T80" s="4">
-        <f t="shared" si="240"/>
+        <f t="shared" si="258"/>
         <v>-22080</v>
       </c>
       <c r="U80" s="4">
-        <f t="shared" si="240"/>
+        <f t="shared" si="258"/>
         <v>-14828</v>
       </c>
       <c r="V80" s="4">
-        <f t="shared" si="240"/>
+        <f t="shared" si="258"/>
         <v>-12580</v>
       </c>
       <c r="W80" s="4">
-        <f t="shared" si="240"/>
+        <f t="shared" si="258"/>
         <v>906</v>
       </c>
       <c r="X80" s="4">
-        <f t="shared" si="240"/>
+        <f t="shared" si="258"/>
         <v>-12078</v>
       </c>
       <c r="Y80" s="4">
-        <f t="shared" si="240"/>
+        <f t="shared" si="258"/>
         <v>-15608</v>
       </c>
       <c r="Z80" s="4">
-        <f t="shared" si="240"/>
+        <f t="shared" si="258"/>
         <v>-10821</v>
       </c>
       <c r="AA80" s="4">
-        <f t="shared" si="240"/>
+        <f t="shared" si="258"/>
         <v>-15806</v>
       </c>
       <c r="AB80" s="4">
-        <f t="shared" si="240"/>
+        <f t="shared" si="258"/>
         <v>-9673</v>
       </c>
       <c r="AC80" s="4">
-        <f t="shared" si="240"/>
+        <f t="shared" si="258"/>
         <v>-11753</v>
       </c>
       <c r="AD80" s="4">
-        <f t="shared" si="240"/>
+        <f t="shared" si="258"/>
         <v>-12601</v>
       </c>
       <c r="AE80" s="4">
-        <f t="shared" si="240"/>
+        <f t="shared" si="258"/>
         <v>-17862</v>
       </c>
       <c r="AF80" s="4">
-        <f t="shared" si="240"/>
+        <f t="shared" si="258"/>
         <v>-22138</v>
       </c>
       <c r="AG80" s="4">
-        <f t="shared" si="240"/>
+        <f t="shared" si="258"/>
         <v>-16899</v>
       </c>
       <c r="AH80" s="4">
-        <f t="shared" si="240"/>
+        <f t="shared" si="258"/>
         <v>-37443</v>
       </c>
       <c r="AI80" s="4">
-        <f t="shared" si="240"/>
+        <f t="shared" si="258"/>
         <v>-29803</v>
       </c>
       <c r="AJ80" s="4">
-        <f t="shared" si="240"/>
+        <f t="shared" si="258"/>
         <v>-39424</v>
       </c>
       <c r="BS80" s="2">
@@ -11670,15 +12078,15 @@
         <v>0</v>
       </c>
       <c r="BS82" s="2">
-        <f t="shared" ref="BS82:BS85" si="241">SUM(W82:Z82)</f>
+        <f t="shared" ref="BS82:BS85" si="259">SUM(W82:Z82)</f>
         <v>-6000</v>
       </c>
       <c r="BT82" s="2">
-        <f t="shared" ref="BT82:BT83" si="242">SUM(AA82:AD82)</f>
+        <f t="shared" ref="BT82:BT83" si="260">SUM(AA82:AD82)</f>
         <v>0</v>
       </c>
       <c r="BU82" s="2">
-        <f t="shared" ref="BU82:BU85" si="243">SUM(AE82:AH82)</f>
+        <f t="shared" ref="BU82:BU85" si="261">SUM(AE82:AH82)</f>
         <v>0</v>
       </c>
     </row>
@@ -11787,15 +12195,15 @@
         <v>-2539</v>
       </c>
       <c r="BS83" s="2">
-        <f t="shared" si="241"/>
+        <f t="shared" si="259"/>
         <v>15718</v>
       </c>
       <c r="BT83" s="2">
-        <f t="shared" si="242"/>
+        <f t="shared" si="260"/>
         <v>-15879</v>
       </c>
       <c r="BU83" s="2">
-        <f t="shared" si="243"/>
+        <f t="shared" si="261"/>
         <v>-11812</v>
       </c>
     </row>
@@ -11816,91 +12224,91 @@
       <c r="M84" s="4"/>
       <c r="N84" s="4"/>
       <c r="O84" s="4">
-        <f t="shared" ref="O84:Q84" si="244">SUM(O82:O83)</f>
+        <f t="shared" ref="O84:Q84" si="262">SUM(O82:O83)</f>
         <v>-2591</v>
       </c>
       <c r="P84" s="4">
-        <f t="shared" si="244"/>
+        <f t="shared" si="262"/>
         <v>7408</v>
       </c>
       <c r="Q84" s="4">
-        <f t="shared" si="244"/>
+        <f t="shared" si="262"/>
         <v>-4105</v>
       </c>
       <c r="R84" s="4">
-        <f t="shared" ref="R84:AJ84" si="245">SUM(R82:R83)</f>
+        <f t="shared" ref="R84:AJ84" si="263">SUM(R82:R83)</f>
         <v>-1816</v>
       </c>
       <c r="S84" s="4">
-        <f t="shared" si="245"/>
+        <f t="shared" si="263"/>
         <v>-3476</v>
       </c>
       <c r="T84" s="4">
-        <f t="shared" si="245"/>
+        <f t="shared" si="263"/>
         <v>15643</v>
       </c>
       <c r="U84" s="4">
-        <f t="shared" si="245"/>
+        <f t="shared" si="263"/>
         <v>-2776</v>
       </c>
       <c r="V84" s="4">
-        <f t="shared" si="245"/>
+        <f t="shared" si="263"/>
         <v>-3100</v>
       </c>
       <c r="W84" s="4">
-        <f t="shared" si="245"/>
+        <f t="shared" si="263"/>
         <v>1990</v>
       </c>
       <c r="X84" s="4">
-        <f t="shared" si="245"/>
+        <f t="shared" si="263"/>
         <v>4626</v>
       </c>
       <c r="Y84" s="4">
-        <f t="shared" si="245"/>
+        <f t="shared" si="263"/>
         <v>3016</v>
       </c>
       <c r="Z84" s="4">
-        <f t="shared" si="245"/>
+        <f t="shared" si="263"/>
         <v>86</v>
       </c>
       <c r="AA84" s="4">
-        <f t="shared" si="245"/>
+        <f t="shared" si="263"/>
         <v>6354</v>
       </c>
       <c r="AB84" s="4">
-        <f t="shared" si="245"/>
+        <f t="shared" si="263"/>
         <v>-6539</v>
       </c>
       <c r="AC84" s="4">
-        <f t="shared" si="245"/>
+        <f t="shared" si="263"/>
         <v>-8948</v>
       </c>
       <c r="AD84" s="4">
-        <f t="shared" si="245"/>
+        <f t="shared" si="263"/>
         <v>-6746</v>
       </c>
       <c r="AE84" s="4">
-        <f t="shared" si="245"/>
+        <f t="shared" si="263"/>
         <v>-1256</v>
       </c>
       <c r="AF84" s="4">
-        <f t="shared" si="245"/>
+        <f t="shared" si="263"/>
         <v>-4490</v>
       </c>
       <c r="AG84" s="4">
-        <f t="shared" si="245"/>
+        <f t="shared" si="263"/>
         <v>-2758</v>
       </c>
       <c r="AH84" s="4">
-        <f t="shared" si="245"/>
+        <f t="shared" si="263"/>
         <v>-3308</v>
       </c>
       <c r="AI84" s="4">
-        <f t="shared" si="245"/>
+        <f t="shared" si="263"/>
         <v>-47</v>
       </c>
       <c r="AJ84" s="4">
-        <f t="shared" si="245"/>
+        <f t="shared" si="263"/>
         <v>-2539</v>
       </c>
       <c r="BS84" s="2">
@@ -11999,7 +12407,7 @@
         <v>1008</v>
       </c>
       <c r="BS85" s="2">
-        <f t="shared" si="241"/>
+        <f t="shared" si="259"/>
         <v>-1093</v>
       </c>
       <c r="BT85" s="2">
@@ -12007,7 +12415,7 @@
         <v>403</v>
       </c>
       <c r="BU85" s="2">
-        <f t="shared" si="243"/>
+        <f t="shared" si="261"/>
         <v>-1301</v>
       </c>
     </row>
@@ -12028,7 +12436,7 @@
       <c r="M86" s="4"/>
       <c r="N86" s="4"/>
       <c r="O86" s="4">
-        <f t="shared" ref="O86" si="246">+O85+O84+O80+O74</f>
+        <f t="shared" ref="O86" si="264">+O85+O84+O80+O74</f>
         <v>-8905</v>
       </c>
       <c r="P86" s="4">
@@ -12040,79 +12448,79 @@
         <v>-7640</v>
       </c>
       <c r="R86" s="4">
-        <f t="shared" ref="R86:AJ86" si="247">+R85+R84+R80+R74</f>
+        <f t="shared" ref="R86:AJ86" si="265">+R85+R84+R80+R74</f>
         <v>12175</v>
       </c>
       <c r="S86" s="4">
-        <f t="shared" si="247"/>
+        <f t="shared" si="265"/>
         <v>-8222</v>
       </c>
       <c r="T86" s="4">
-        <f t="shared" si="247"/>
+        <f t="shared" si="265"/>
         <v>6512</v>
       </c>
       <c r="U86" s="4">
-        <f t="shared" si="247"/>
+        <f t="shared" si="265"/>
         <v>-10490</v>
       </c>
       <c r="V86" s="4">
-        <f t="shared" si="247"/>
+        <f t="shared" si="265"/>
         <v>6300</v>
       </c>
       <c r="W86" s="4">
-        <f t="shared" si="247"/>
+        <f t="shared" si="265"/>
         <v>122</v>
       </c>
       <c r="X86" s="4">
-        <f t="shared" si="247"/>
+        <f t="shared" si="265"/>
         <v>1101</v>
       </c>
       <c r="Y86" s="4">
-        <f t="shared" si="247"/>
+        <f t="shared" si="265"/>
         <v>-2522</v>
       </c>
       <c r="Z86" s="4">
-        <f t="shared" si="247"/>
+        <f t="shared" si="265"/>
         <v>19075</v>
       </c>
       <c r="AA86" s="4">
-        <f t="shared" si="247"/>
+        <f t="shared" si="265"/>
         <v>-4519</v>
       </c>
       <c r="AB86" s="4">
-        <f t="shared" si="247"/>
+        <f t="shared" si="265"/>
         <v>333</v>
       </c>
       <c r="AC86" s="4">
-        <f t="shared" si="247"/>
+        <f t="shared" si="265"/>
         <v>14</v>
       </c>
       <c r="AD86" s="4">
-        <f t="shared" si="247"/>
+        <f t="shared" si="265"/>
         <v>23809</v>
       </c>
       <c r="AE86" s="4">
-        <f t="shared" si="247"/>
+        <f t="shared" si="265"/>
         <v>-558</v>
       </c>
       <c r="AF86" s="4">
-        <f t="shared" si="247"/>
+        <f t="shared" si="265"/>
         <v>-1659</v>
       </c>
       <c r="AG86" s="4">
-        <f t="shared" si="247"/>
+        <f t="shared" si="265"/>
         <v>7004</v>
       </c>
       <c r="AH86" s="4">
-        <f t="shared" si="247"/>
+        <f t="shared" si="265"/>
         <v>3635</v>
       </c>
       <c r="AI86" s="4">
-        <f t="shared" si="247"/>
+        <f t="shared" si="265"/>
         <v>-12419</v>
       </c>
       <c r="AJ86" s="4">
-        <f t="shared" si="247"/>
+        <f t="shared" si="265"/>
         <v>-8440</v>
       </c>
       <c r="BS86" s="2">
@@ -12543,51 +12951,51 @@
         <v>102</v>
       </c>
       <c r="O95" s="4">
-        <f t="shared" ref="O95:W95" si="248">+O74+O76+O77</f>
+        <f t="shared" ref="O95:W95" si="266">+O74+O76+O77</f>
         <v>-2364</v>
       </c>
       <c r="P95" s="4">
-        <f t="shared" si="248"/>
+        <f t="shared" si="266"/>
         <v>13991</v>
       </c>
       <c r="Q95" s="4">
-        <f t="shared" si="248"/>
+        <f t="shared" si="266"/>
         <v>2156</v>
       </c>
       <c r="R95" s="4">
-        <f t="shared" si="248"/>
+        <f t="shared" si="266"/>
         <v>17235</v>
       </c>
       <c r="S95" s="4">
-        <f t="shared" si="248"/>
+        <f t="shared" si="266"/>
         <v>-6974</v>
       </c>
       <c r="T95" s="4">
-        <f t="shared" si="248"/>
+        <f t="shared" si="266"/>
         <v>-273</v>
       </c>
       <c r="U95" s="4">
-        <f t="shared" si="248"/>
+        <f t="shared" si="266"/>
         <v>-7438</v>
       </c>
       <c r="V95" s="4">
-        <f t="shared" si="248"/>
+        <f t="shared" si="266"/>
         <v>5616</v>
       </c>
       <c r="W95" s="4">
-        <f t="shared" si="248"/>
+        <f t="shared" si="266"/>
         <v>-16532</v>
       </c>
       <c r="X95" s="4">
-        <f t="shared" ref="X95:Z95" si="249">+X74+X76+X77</f>
+        <f t="shared" ref="X95:Z95" si="267">+X74+X76+X77</f>
         <v>-5133</v>
       </c>
       <c r="Y95" s="4">
-        <f t="shared" si="249"/>
+        <f t="shared" si="267"/>
         <v>-3637</v>
       </c>
       <c r="Z95" s="4">
-        <f t="shared" si="249"/>
+        <f t="shared" si="267"/>
         <v>13733</v>
       </c>
       <c r="AA95" s="4">
@@ -12595,31 +13003,31 @@
         <v>-8282</v>
       </c>
       <c r="AB95" s="4">
-        <f t="shared" ref="AB95:AE95" si="250">+AB74+AB76+AB77</f>
+        <f t="shared" ref="AB95:AE95" si="268">+AB74+AB76+AB77</f>
         <v>6064</v>
       </c>
       <c r="AC95" s="4">
-        <f t="shared" si="250"/>
+        <f t="shared" si="268"/>
         <v>9919</v>
       </c>
       <c r="AD95" s="4">
-        <f t="shared" si="250"/>
+        <f t="shared" si="268"/>
         <v>29112</v>
       </c>
       <c r="AE95" s="4">
-        <f t="shared" si="250"/>
+        <f t="shared" si="268"/>
         <v>5054</v>
       </c>
       <c r="AF95" s="4">
-        <f t="shared" ref="AF95:AH95" si="251">+AF74+AF76+AF77</f>
+        <f t="shared" ref="AF95:AH95" si="269">+AF74+AF76+AF77</f>
         <v>8888</v>
       </c>
       <c r="AG95" s="4">
-        <f t="shared" si="251"/>
+        <f t="shared" si="269"/>
         <v>4693</v>
       </c>
       <c r="AH95" s="4">
-        <f t="shared" si="251"/>
+        <f t="shared" si="269"/>
         <v>19584</v>
       </c>
       <c r="AI95" s="4">
@@ -12644,15 +13052,15 @@
         <v>107</v>
       </c>
       <c r="R96" s="2">
-        <f t="shared" ref="R96:T96" si="252">SUM(O95:R95)</f>
+        <f t="shared" ref="R96:T96" si="270">SUM(O95:R95)</f>
         <v>31018</v>
       </c>
       <c r="S96" s="2">
-        <f t="shared" si="252"/>
+        <f t="shared" si="270"/>
         <v>26408</v>
       </c>
       <c r="T96" s="2">
-        <f t="shared" si="252"/>
+        <f t="shared" si="270"/>
         <v>12144</v>
       </c>
       <c r="U96" s="2">
@@ -12672,7 +13080,7 @@
         <v>-23487</v>
       </c>
       <c r="Y96" s="2">
-        <f t="shared" ref="Y96" si="253">SUM(V95:Y95)</f>
+        <f t="shared" ref="Y96" si="271">SUM(V95:Y95)</f>
         <v>-19686</v>
       </c>
       <c r="Z96" s="2">
@@ -12684,31 +13092,31 @@
         <v>-3319</v>
       </c>
       <c r="AB96" s="5">
-        <f t="shared" ref="AB96:AE96" si="254">SUM(Y95:AB95)</f>
+        <f t="shared" ref="AB96:AE96" si="272">SUM(Y95:AB95)</f>
         <v>7878</v>
       </c>
       <c r="AC96" s="5">
-        <f t="shared" si="254"/>
+        <f t="shared" si="272"/>
         <v>21434</v>
       </c>
       <c r="AD96" s="5">
-        <f t="shared" si="254"/>
+        <f t="shared" si="272"/>
         <v>36813</v>
       </c>
       <c r="AE96" s="5">
-        <f t="shared" si="254"/>
+        <f t="shared" si="272"/>
         <v>50149</v>
       </c>
       <c r="AF96" s="5">
-        <f t="shared" ref="AF96:AH96" si="255">SUM(AC95:AF95)</f>
+        <f t="shared" ref="AF96:AH96" si="273">SUM(AC95:AF95)</f>
         <v>52973</v>
       </c>
       <c r="AG96" s="5">
-        <f t="shared" si="255"/>
+        <f t="shared" si="273"/>
         <v>47747</v>
       </c>
       <c r="AH96" s="5">
-        <f t="shared" si="255"/>
+        <f t="shared" si="273"/>
         <v>38219</v>
       </c>
       <c r="AI96" s="5">
